--- a/update_data_folder/WordList.xlsx
+++ b/update_data_folder/WordList.xlsx
@@ -6646,47 +6646,47 @@
         <v>vocab-food</v>
       </c>
       <c r="B2" t="str">
-        <v>mushroom</v>
+        <v>beef</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>vocab-places</v>
+        <v>vocab-animal</v>
       </c>
       <c r="B3" t="str">
-        <v>airport</v>
+        <v>bird</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>vocab-animal</v>
+        <v>vocab-body</v>
       </c>
       <c r="B4" t="str">
-        <v>pig</v>
+        <v>hand</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>vocab-body</v>
+        <v>vocab-clothes</v>
       </c>
       <c r="B5" t="str">
-        <v>eye</v>
+        <v>hat</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>vocab-clothes</v>
+        <v>vocab-colors</v>
       </c>
       <c r="B6" t="str">
-        <v>pants</v>
+        <v>pink</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>vocab-colors</v>
+        <v>vocab-places</v>
       </c>
       <c r="B7" t="str">
-        <v>yellow</v>
+        <v>bank</v>
       </c>
     </row>
     <row r="8">
@@ -6694,31 +6694,31 @@
         <v>oral-everyday</v>
       </c>
       <c r="B8" t="str">
-        <v>orange</v>
+        <v>cake</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>oral-opinions</v>
+        <v>oral-food</v>
       </c>
       <c r="B9" t="str">
-        <v>cherry</v>
+        <v>beef</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>oral-food</v>
+        <v>oral-emotions</v>
       </c>
       <c r="B10" t="str">
-        <v>hungry</v>
+        <v>bear</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>oral-emotions</v>
+        <v>oral-opinions</v>
       </c>
       <c r="B11" t="str">
-        <v>durian</v>
+        <v>elephant</v>
       </c>
     </row>
   </sheetData>

--- a/update_data_folder/WordList.xlsx
+++ b/update_data_folder/WordList.xlsx
@@ -729,7 +729,7 @@
         <v>Animals</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="str">
         <v>海鸥</v>
@@ -799,7 +799,7 @@
         <v>Food</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="str">
         <v>榴莲</v>
@@ -1427,7 +1427,7 @@
         <v>Food</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="str">
         <v>西兰花</v>
@@ -2111,7 +2111,7 @@
         <v>Body</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" t="str">
         <v>骷髅</v>
@@ -2377,7 +2377,7 @@
         <v>Clothes</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="str">
         <v>凉鞋</v>
@@ -2675,7 +2675,7 @@
         <v>Purple Cabbage is wearing too many layers and can't take them off!</v>
       </c>
       <c r="C62" t="str">
-        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round purple cabbage with a frustrated face, wrapped in many ruffled leafy layers bulging outward"</v>
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round purple cabbage with a frustrated face, wrapped in many ruffled leafy layers bulging outward, purely purple color"</v>
       </c>
       <c r="D62" t="str">
         <v>Colors</v>
@@ -2751,7 +2751,7 @@
         <v>White Snowman is eating an ice pop to stay cool!</v>
       </c>
       <c r="C64" t="str">
-        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round white snowman with a happy relaxed face, wearing a top hat and a tiny striped scarf, holding a blue ice pop"</v>
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round white snowman with a happy relaxed face, wearing a top hat and a tiny striped scarf, holding a blue ice pop, no legs no foot"</v>
       </c>
       <c r="D64" t="str">
         <v>Colors</v>
@@ -3321,7 +3321,7 @@
         <v>Ice Cream is crowning herself queen with her cone hat!</v>
       </c>
       <c r="C79" t="str">
-        <v>PlushStyle, plush style, high resolution, rich and elaborate details, white background, a super cute plush toy of "a pink ice cream with a smug smile, lifting her waffle cone like a royal crown"</v>
+        <v>PlushStyle, plush style, high resolution, rich and elaborate details, white background, a super cute plush toy of "a pink ice cream with a smug queenly face, placing her upside-down waffle cone on top like a crown"</v>
       </c>
       <c r="D79" t="str">
         <v>Food</v>
@@ -3707,7 +3707,7 @@
         <v>Food</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" t="str">
         <v>海藻</v>
@@ -3777,7 +3777,7 @@
         <v>Soup is hiding from the big scary spoon!</v>
       </c>
       <c r="C91" t="str">
-        <v>PlushStyle, plush style, high resolution, rich and elaborate details, white background, a super cute plush toy of "a small soup bowl with a panicked face, hiding behind a napkin, a large spoon looming close"</v>
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a small soup bowl with a frightened face peeking out, a large spoon looming over it"</v>
       </c>
       <c r="D91" t="str">
         <v>Food</v>
@@ -3812,7 +3812,10 @@
         <v>steak</v>
       </c>
       <c r="B92" t="str">
-        <v>Steak is flexing his juicy muscles on the plate!</v>
+        <v>The steak feels so cozy wrapped in its pastry blanket — beef Wellington style.</v>
+      </c>
+      <c r="C92" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a thick steak snugly wrapped in a golden pastry crust like a blanket, with a cozy sleepy smile"</v>
       </c>
       <c r="D92" t="str">
         <v>Food</v>
@@ -3847,7 +3850,10 @@
         <v>sunflower</v>
       </c>
       <c r="B93" t="str">
-        <v>Sunflower has a sore neck from her giant heavy head!</v>
+        <v>The sunflower has a stiff neck from staring at the sun all day.</v>
+      </c>
+      <c r="C93" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a tall sunflower tilting its big flower head to one side with a tired face, a tiny bright sun in the corner"</v>
       </c>
       <c r="D93" t="str">
         <v>Food</v>
@@ -3882,7 +3888,10 @@
         <v>tea</v>
       </c>
       <c r="B94" t="str">
-        <v>Tea is splashing in her hot tub with a teabag floaty!</v>
+        <v>The tea bag starts spilling all the gossip the moment it hits hot water.</v>
+      </c>
+      <c r="C94" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a tea bag sitting in a small cup of light green tea with a chatty excited face, a speech bubble with '!' next to it, having little cute feet"</v>
       </c>
       <c r="D94" t="str">
         <v>Food</v>
@@ -3917,7 +3926,10 @@
         <v>tomato</v>
       </c>
       <c r="B95" t="str">
-        <v>Tomato is sneaking into the fruit club in a fake mustache.</v>
+        <v>The tomato turns even redder when it's embarrassed.</v>
+      </c>
+      <c r="C95" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round deep-red tomato covering its cheeks with tiny hands, with a shy blushing face"</v>
       </c>
       <c r="D95" t="str">
         <v>Food</v>
@@ -3952,7 +3964,10 @@
         <v>water</v>
       </c>
       <c r="B96" t="str">
-        <v>Water spills herself on purpose just to steal the spotlight.</v>
+        <v>The water can never keep a secret — it's completely see-through.</v>
+      </c>
+      <c r="C96" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a tall clear glass of water with a nervous embarrassed face, a tiny key visible inside its transparent body"</v>
       </c>
       <c r="D96" t="str">
         <v>Food</v>
@@ -3987,7 +4002,10 @@
         <v>bag</v>
       </c>
       <c r="B97" t="str">
-        <v>Bag swallowed the keys again and is playing dumb.</v>
+        <v>The bag ate too much and now the zipper won't close.</v>
+      </c>
+      <c r="C97" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round overstuffed backpack with a bursting open zipper, with a guilty satisfied face"</v>
       </c>
       <c r="D97" t="str">
         <v>Items</v>
@@ -4022,7 +4040,10 @@
         <v>bed</v>
       </c>
       <c r="B98" t="str">
-        <v>Bed is giving the warmest hug in the whole house.</v>
+        <v>The bed is so sleepy — everyone naps on it but nobody lets it rest.</v>
+      </c>
+      <c r="C98" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a small bed with half-closed drowsy eyes on the headboard, a sleepy yawning face, ZZZ floating above"</v>
       </c>
       <c r="D98" t="str">
         <v>Items</v>
@@ -4057,7 +4078,10 @@
         <v>book</v>
       </c>
       <c r="B99" t="str">
-        <v>Book keeps dozing off and closing herself mid-story.</v>
+        <v>The book is so thick it's out of breath halfway through.</v>
+      </c>
+      <c r="C99" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a very thick closed book with a bookmark poking out halfway, with an exhausted panting face on the cover and tiny sweat drops"</v>
       </c>
       <c r="D99" t="str">
         <v>Items</v>
@@ -4092,7 +4116,10 @@
         <v>bowl</v>
       </c>
       <c r="B100" t="str">
-        <v>Bowl is slurping up his own soup when nobody's looking!</v>
+        <v>The bowl thinks it's a swimming pool every time it's filled with soup.</v>
+      </c>
+      <c r="C100" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round blue bowl wearing tiny sunglasses with a chill face, a few small vegetables floating in light yellow soup like swimmers, having little cute feet"</v>
       </c>
       <c r="D100" t="str">
         <v>Items</v>
@@ -4129,11 +4156,14 @@
       <c r="B101" t="str">
         <v>Calculator is judging everyone's math with a smug little face.</v>
       </c>
+      <c r="C101" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a calculator with a smug face, chin slightly raised, eyes half-closed in a judging look"</v>
+      </c>
       <c r="D101" t="str">
         <v>Items</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" t="str">
         <v>计算器</v>
@@ -4164,6 +4194,9 @@
       <c r="B102" t="str">
         <v>Camera keeps taking selfies with her own flash!</v>
       </c>
+      <c r="C102" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a camera with its flash popping bright, holding a tiny mirror with a dazzled grinning face"</v>
+      </c>
       <c r="D102" t="str">
         <v>Items</v>
       </c>
@@ -4199,6 +4232,9 @@
       <c r="B103" t="str">
         <v>Chair is SO tired of holding everyone's heavy bottoms!</v>
       </c>
+      <c r="C103" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a wooden chair with shaky wobbly legs, with an exhausted annoyed face and tiny sweat drops"</v>
+      </c>
       <c r="D103" t="str">
         <v>Items</v>
       </c>
@@ -4234,6 +4270,9 @@
       <c r="B104" t="str">
         <v>Charger is giving his phone friend a big energy hug!</v>
       </c>
+      <c r="C104" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a charger cable wrapping around a small phone like a hug, both with happy smiling faces"</v>
+      </c>
       <c r="D104" t="str">
         <v>Items</v>
       </c>
@@ -4269,6 +4308,9 @@
       <c r="B105" t="str">
         <v>Computer has 47 tabs open and a splitting headache!</v>
       </c>
+      <c r="C105" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a laptop with many tiny tabs popping out of the screen, with a pained headache face and a small ice pack on top"</v>
+      </c>
       <c r="D105" t="str">
         <v>Items</v>
       </c>
@@ -4304,6 +4346,9 @@
       <c r="B106" t="str">
         <v>Cup is holding her breath so the water won't spill!</v>
       </c>
+      <c r="C106" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a cup filled to the very brim with water, puffing its cheeks with a nervous tense face"</v>
+      </c>
       <c r="D106" t="str">
         <v>Items</v>
       </c>
@@ -4339,6 +4384,9 @@
       <c r="B107" t="str">
         <v>Door is sick of being slammed and wants an apology!</v>
       </c>
+      <c r="C107" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a wooden door with an angry pouty face, one small arm crossed, a red bump mark on its edge"</v>
+      </c>
       <c r="D107" t="str">
         <v>Items</v>
       </c>
@@ -4374,6 +4422,9 @@
       <c r="B108" t="str">
         <v>Fork is poking everything just to say hi!</v>
       </c>
+      <c r="C108" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a silver fork with a cheerful eager face, poking a tiny round tomato with its prongs"</v>
+      </c>
       <c r="D108" t="str">
         <v>Items</v>
       </c>
@@ -4409,6 +4460,9 @@
       <c r="B109" t="str">
         <v>Headphones are whispering secrets straight into your ears!</v>
       </c>
+      <c r="C109" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a pair of headphones with a mischievous whispering face, a tiny speech bubble with '🤫' between the ear cups"</v>
+      </c>
       <c r="D109" t="str">
         <v>Items</v>
       </c>
@@ -4444,6 +4498,9 @@
       <c r="B110" t="str">
         <v>Key thinks every lock is a puzzle only she can solve.</v>
       </c>
+      <c r="C110" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a detective-style golden key with a confident smirk, standing next to a small padlock with a puzzled face"</v>
+      </c>
       <c r="D110" t="str">
         <v>Items</v>
       </c>
@@ -4479,6 +4536,9 @@
       <c r="B111" t="str">
         <v>Knife is bragging about being the sharpest one in the drawer!</v>
       </c>
+      <c r="C111" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a shiny kitchen knife with a proud smirk and chin raised, standing on a small open drawer"</v>
+      </c>
       <c r="D111" t="str">
         <v>Items</v>
       </c>
@@ -4514,6 +4574,9 @@
       <c r="B112" t="str">
         <v>Laptop is burning up from binge-watching cat videos all night!</v>
       </c>
+      <c r="C112" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a laptop with a red overheated face, a tiny cat icon on its screen, small heat waves rising from the top"</v>
+      </c>
       <c r="D112" t="str">
         <v>Items</v>
       </c>
@@ -4546,6 +4609,9 @@
       <c r="B113" t="str">
         <v>Map is lost and too embarrassed to ask for directions!</v>
       </c>
+      <c r="C113" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a folded map with colorful route lines on it, held upside-down with a confused embarrassed face, tiny sweat drops and a '?' above"</v>
+      </c>
       <c r="D113" t="str">
         <v>Items</v>
       </c>
@@ -4566,6 +4632,9 @@
       </c>
       <c r="J113" t="str">
         <v>/mæp/</v>
+      </c>
+      <c r="K113" t="str">
+        <v>地图自己迷路了，还不好意思开口问路！</v>
       </c>
       <c r="L113" t="str">
         <v>ちずくんがまいごになっちゃったの。でも、ひとにみちをきくのがはずかしくて、じっとしてるんだって。</v>
@@ -4578,6 +4647,9 @@
       <c r="B114" t="str">
         <v>Money is hiding in the couch cushions for a secret vacation!</v>
       </c>
+      <c r="C114" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a green dollar bill with sunglasses and a relaxed happy face, hiding inside a small sofa gap"</v>
+      </c>
       <c r="D114" t="str">
         <v>Items</v>
       </c>
@@ -4598,6 +4670,9 @@
       </c>
       <c r="J114" t="str">
         <v>/ˈmʌni/</v>
+      </c>
+      <c r="K114" t="str">
+        <v>钞票偷偷躲在沙发垫里，计划一场秘密度假！</v>
       </c>
       <c r="L114" t="str">
         <v>おかねちゃんがソファーのすきまにかくれて、ないしょのばかんすをしてるの。</v>
@@ -4610,6 +4685,9 @@
       <c r="B115" t="str">
         <v>Phone keeps pocket-dialing everyone and blaming the pants.</v>
       </c>
+      <c r="C115" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a phone with a cheeky innocent face poking out of a jeans pocket, the pocket with an annoyed face"</v>
+      </c>
       <c r="D115" t="str">
         <v>Items</v>
       </c>
@@ -4630,6 +4708,9 @@
       </c>
       <c r="J115" t="str">
         <v>/foʊn/</v>
+      </c>
+      <c r="K115" t="str">
+        <v>手机总误拨电话给所有人，还赖是裤子的锅。</v>
       </c>
       <c r="L115" t="str">
         <v>けいたいくんがポケットのなかでだれかにかけちゃって、それをズボンのせいにしてるんだ。</v>
@@ -4642,6 +4723,9 @@
       <c r="B116" t="str">
         <v>Plate is showing off her fancy gold rim like a new necklace.</v>
       </c>
+      <c r="C116" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round white plate with a shiny gold rim, with a proud glamorous face, tilting slightly to show off the rim"</v>
+      </c>
       <c r="D116" t="str">
         <v>Items</v>
       </c>
@@ -4662,6 +4746,9 @@
       </c>
       <c r="J116" t="str">
         <v>/pleɪt/</v>
+      </c>
+      <c r="K116" t="str">
+        <v>盘子炫耀自己漂亮的金边，像戴了条新项链。</v>
       </c>
       <c r="L116" t="str">
         <v>おさらちゃんがきれいなきんのふちを、あたらしいネックレスみたいにみせびらかしてるの。</v>
@@ -4674,6 +4761,9 @@
       <c r="B117" t="str">
         <v>Saw keeps falling asleep mid-cut and snoring "zzzzzz"!</v>
       </c>
+      <c r="C117" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a handsaw resting on a half-cut piece of wood, with closed sleepy eyes and ZZZ floating above"</v>
+      </c>
       <c r="D117" t="str">
         <v>Items</v>
       </c>
@@ -4694,6 +4784,9 @@
       </c>
       <c r="J117" t="str">
         <v>/sɔː/</v>
+      </c>
+      <c r="K117" t="str">
+        <v>锯子锯到一半就睡着，还打起了呼噜！</v>
       </c>
       <c r="L117" t="str">
         <v>のこぎりくんがきりかけでねむっちゃって、「すーすー」ないてるんだ。</v>
@@ -4706,6 +4799,9 @@
       <c r="B118" t="str">
         <v>Scale is lying about everyone's weight just to make friends.</v>
       </c>
+      <c r="C118" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a bathroom scale with a sneaky winking face, its display showing a tiny number with a speech bubble '😉'"</v>
+      </c>
       <c r="D118" t="str">
         <v>Items</v>
       </c>
@@ -4726,6 +4822,9 @@
       </c>
       <c r="J118" t="str">
         <v>/skeɪl/</v>
+      </c>
+      <c r="K118" t="str">
+        <v>体重秤为了交朋友，对每个人的体重都撒了谎。</v>
       </c>
       <c r="L118" t="str">
         <v>たいじょうけいくんがみんなのたいじゅうをうそついて、ともだちをつくろうとしてるの。</v>
@@ -4738,6 +4837,9 @@
       <c r="B119" t="str">
         <v>Scarecrow is posing all day and calling it "modeling."</v>
       </c>
+      <c r="C119" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a scarecrow with a fashionable confident face, one arm out in a model pose, wearing a tiny straw hat"</v>
+      </c>
       <c r="D119" t="str">
         <v>Items</v>
       </c>
@@ -4758,6 +4860,9 @@
       </c>
       <c r="J119" t="str">
         <v>/ˈskɛrkroʊ/</v>
+      </c>
+      <c r="K119" t="str">
+        <v>稻草人整天摆姿势，还管这叫"走台步"。</v>
       </c>
       <c r="L119" t="str">
         <v>かかしさんがいちにちじゅうポーズをとって、それを「モデル」のしごとだっておもってるんだって。</v>
@@ -4770,6 +4875,9 @@
       <c r="B120" t="str">
         <v>Scissors only get things done when they finally shut up!</v>
       </c>
+      <c r="C120" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a pair of scissors with a smug satisfied face on the handle, blades closed tight, snipping a piece of paper"</v>
+      </c>
       <c r="D120" t="str">
         <v>Items</v>
       </c>
@@ -4790,6 +4898,9 @@
       </c>
       <c r="J120" t="str">
         <v>/ˈsɪzərz/</v>
+      </c>
+      <c r="K120" t="str">
+        <v>剪刀只有闭上嘴，才能真正办成事！</v>
       </c>
       <c r="L120" t="str">
         <v>はさみくんはやっとおしゃべりをやめたときに、やっとしごとができるんだって。</v>
@@ -4802,11 +4913,14 @@
       <c r="B121" t="str">
         <v>Screwdriver thinks every problem just needs one more twist.</v>
       </c>
+      <c r="C121" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a screwdriver with a determined confident face, pressing down on a tiny screw with a speech bubble '1 more!'"</v>
+      </c>
       <c r="D121" t="str">
         <v>Items</v>
       </c>
       <c r="E121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" t="str">
         <v>螺丝刀</v>
@@ -4822,6 +4936,9 @@
       </c>
       <c r="J121" t="str">
         <v>/ˈskruːˌdraɪvər/</v>
+      </c>
+      <c r="K121" t="str">
+        <v>螺丝刀觉得所有问题都只需要再拧一下。</v>
       </c>
       <c r="L121" t="str">
         <v>ねじまわしくんは、どんなこまったことも、もういっかいまげばなんとかなるっておもってるの。</v>
@@ -4834,6 +4951,9 @@
       <c r="B122" t="str">
         <v>Shell carries her house everywhere, just in case she needs a nap!</v>
       </c>
+      <c r="C122" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a fancily accessorized seashell half-open like a bed, with a cozy sleepy face peeking out, ZZZ floating above"</v>
+      </c>
       <c r="D122" t="str">
         <v>Items</v>
       </c>
@@ -4869,6 +4989,9 @@
       <c r="B123" t="str">
         <v>Shield never peeks at what's flying toward him!</v>
       </c>
+      <c r="C123" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a round metal shield with eyes squeezed shut and a scared face, a tiny arrow stuck on its surface"</v>
+      </c>
       <c r="D123" t="str">
         <v>Items</v>
       </c>
@@ -4904,6 +5027,9 @@
       <c r="B124" t="str">
         <v>Shovel keeps digging up secrets nobody asked for!</v>
       </c>
+      <c r="C124" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a shovel with a mischievous gossipy face, digging into a small dirt pile with a speech bubble '👀'"</v>
+      </c>
       <c r="D124" t="str">
         <v>Items</v>
       </c>
@@ -4939,6 +5065,9 @@
       <c r="B125" t="str">
         <v>Sock ran away from the laundry to live a single life!</v>
       </c>
+      <c r="C125" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a single colorful sock with a happy free-spirited face, wearing tiny sunglasses, both small arms raised in a cheerful wave"</v>
+      </c>
       <c r="D125" t="str">
         <v>Items</v>
       </c>
@@ -4974,6 +5103,9 @@
       <c r="B126" t="str">
         <v>Sofa has swallowed three remotes and isn't giving them back!</v>
       </c>
+      <c r="C126" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a plump sofa with a cheeky grinning face, three remote corners poking out between its cushions"</v>
+      </c>
       <c r="D126" t="str">
         <v>Items</v>
       </c>
@@ -5009,6 +5141,9 @@
       <c r="B127" t="str">
         <v>Spoon is jealous that Fork gets all the fun poking jobs!</v>
       </c>
+      <c r="C127" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a spoon with a jealous pouty face, watching a small fork happily poking a tiny piece of food"</v>
+      </c>
       <c r="D127" t="str">
         <v>Items</v>
       </c>
@@ -5044,6 +5179,9 @@
       <c r="B128" t="str">
         <v>Stethoscope is eavesdropping on everyone's heartbeat gossip!</v>
       </c>
+      <c r="C128" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a stethoscope with a nosy eager face on the chest piece, leaning against a tiny red heart with a surprised face"</v>
+      </c>
       <c r="D128" t="str">
         <v>Items</v>
       </c>
@@ -5079,6 +5217,9 @@
       <c r="B129" t="str">
         <v>Suitcase ate too many clothes and can't zip up!</v>
       </c>
+      <c r="C129" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "an overstuffed suitcase with a zipper bursting open, clothes peeking out, with a guilty bloated face"</v>
+      </c>
       <c r="D129" t="str">
         <v>Items</v>
       </c>
@@ -5101,7 +5242,7 @@
         <v>/ˈsuːtkeɪs/</v>
       </c>
       <c r="K129" t="str">
-        <v>行李箱衣服吃撑了，拉链都拉不上啦！</v>
+        <v>行李箱衣服吃撑了，拉链都拉不上了！</v>
       </c>
       <c r="L129" t="str">
         <v>スーツケースくんがふくをたべすぎて、チャックがしまらないんだって！</v>
@@ -5114,6 +5255,9 @@
       <c r="B130" t="str">
         <v>Table is wobbling her bad leg for attention again!</v>
       </c>
+      <c r="C130" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a small wooden table with one shorter wobbly leg, with a dramatic whiny face, tilting to one side"</v>
+      </c>
       <c r="D130" t="str">
         <v>Items</v>
       </c>
@@ -5149,6 +5293,9 @@
       <c r="B131" t="str">
         <v>Telescope is stretching his long neck to spy on the moon.</v>
       </c>
+      <c r="C131" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a detective-style telescope with its tube stretched out long, with a nosy curious face, a tiny moon in the corner"</v>
+      </c>
       <c r="D131" t="str">
         <v>Items</v>
       </c>
@@ -5184,6 +5331,9 @@
       <c r="B132" t="str">
         <v>Tent is holding his breath so he won't collapse!</v>
       </c>
+      <c r="C132" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a green triangular tent puffing its cheeks hard with a tense nervous face, slightly inflated, having little cute feet"</v>
+      </c>
       <c r="D132" t="str">
         <v>Items</v>
       </c>
@@ -5219,6 +5369,9 @@
       <c r="B133" t="str">
         <v>Throne refuses to let anyone sit without a royal appointment!</v>
       </c>
+      <c r="C133" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a Victorian-style golden throne with a snooty proud face, one small arm raised in a 'stop' gesture"</v>
+      </c>
       <c r="D133" t="str">
         <v>Items</v>
       </c>
@@ -5254,6 +5407,9 @@
       <c r="B134" t="str">
         <v>Ticket is terrified of getting ripped in half on his big day!</v>
       </c>
+      <c r="C134" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a colorful ticket with a sad worried face, a tiny dotted tear-line across its middle, trembling with sweat drops, having little cute feet"</v>
+      </c>
       <c r="D134" t="str">
         <v>Items</v>
       </c>
@@ -5289,6 +5445,9 @@
       <c r="B135" t="str">
         <v>Toaster keeps scaring himself every time the bread pops out!</v>
       </c>
+      <c r="C135" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a toaster with a shocked startled face, a piece of toast popping out of the top, having little cute feet"</v>
+      </c>
       <c r="D135" t="str">
         <v>Items</v>
       </c>
@@ -5324,6 +5483,9 @@
       <c r="B136" t="str">
         <v>Toothbrush thinks her messy bristles are a punk hairstyle!</v>
       </c>
+      <c r="C136" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a punk-style toothbrush with wild spiky bristles sticking out in all directions, with a proud cool face"</v>
+      </c>
       <c r="D136" t="str">
         <v>Items</v>
       </c>
@@ -5359,6 +5521,9 @@
       <c r="B137" t="str">
         <v>Trophy won't stop polishing himself for the perfect shine!</v>
       </c>
+      <c r="C137" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a shiny golden trophy holding a tiny cloth, polishing itself with a vain satisfied face, having little cute feet"</v>
+      </c>
       <c r="D137" t="str">
         <v>Items</v>
       </c>
@@ -5394,6 +5559,9 @@
       <c r="B138" t="str">
         <v>TV is mad nobody looks her in the eye anymore — just phones!</v>
       </c>
+      <c r="C138" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a retro-style TV with an angry jealous face on the screen, a tiny smartphone next to it getting all the attention, having little cute feet"</v>
+      </c>
       <c r="D138" t="str">
         <v>Items</v>
       </c>
@@ -5429,6 +5597,9 @@
       <c r="B139" t="str">
         <v>Umbrella is sulking in the corner waiting for a rainy day!</v>
       </c>
+      <c r="C139" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a floral-pattern umbrella with a lonely pouty face, a tiny thought bubble with a rain cloud"</v>
+      </c>
       <c r="D139" t="str">
         <v>Items</v>
       </c>
@@ -5464,6 +5635,9 @@
       <c r="B140" t="str">
         <v>Wallet is on a diet because no money ever comes in!</v>
       </c>
+      <c r="C140" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a very flat thin wallet with a sad hungry face, a tiny belt tightened around it, having little cute feet"</v>
+      </c>
       <c r="D140" t="str">
         <v>Items</v>
       </c>
@@ -5499,6 +5673,9 @@
       <c r="B141" t="str">
         <v>Watering Can has a runny nose that won't stop dripping!</v>
       </c>
+      <c r="C141" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a green watering can with a runny dripping spout, with a sniffly uncomfortable face, having little cute feet"</v>
+      </c>
       <c r="D141" t="str">
         <v>Items</v>
       </c>
@@ -5534,6 +5711,9 @@
       <c r="B142" t="str">
         <v>Window is tired of people only looking through her, never at her!</v>
       </c>
+      <c r="C142" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a Victorian-style window with a sad neglected face on the glass pane, tiny arms crossed with a pouty look"</v>
+      </c>
       <c r="D142" t="str">
         <v>Items</v>
       </c>
@@ -5569,6 +5749,9 @@
       <c r="B143" t="str">
         <v>Cloud is shape-shifting into a bunny to get more likes!</v>
       </c>
+      <c r="C143" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a fluffy white cloud shaped like a bunny with cloud-shaped ears, with a pleased hopeful face, tiny heart-shaped likes floating around"</v>
+      </c>
       <c r="D143" t="str">
         <v>Nature</v>
       </c>
@@ -5604,6 +5787,9 @@
       <c r="B144" t="str">
         <v>Rain keeps knocking on the window but nobody lets him in!</v>
       </c>
+      <c r="C144" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a blue raindrop with a sad pleading face, behind a small window, having little cute feet"</v>
+      </c>
       <c r="D144" t="str">
         <v>Nature</v>
       </c>
@@ -5639,6 +5825,9 @@
       <c r="B145" t="str">
         <v>Snow is an artist, painting everything white.</v>
       </c>
+      <c r="C145" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "an artist-style round snowball holding a paintbrush dripping white paint, with a proud creative face, having little cute feet"</v>
+      </c>
       <c r="D145" t="str">
         <v>Nature</v>
       </c>
@@ -5674,6 +5863,9 @@
       <c r="B146" t="str">
         <v>Snowflake insists she looks nothing like her billion sisters!</v>
       </c>
+      <c r="C146" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a sparkly snowflake with a sassy confident face, next to two identical smaller snowflakes with confused faces, having little cute feet"</v>
+      </c>
       <c r="D146" t="str">
         <v>Nature</v>
       </c>
@@ -5709,6 +5901,9 @@
       <c r="B147" t="str">
         <v>Sun forgot his sunglasses and is squinting at everyone!</v>
       </c>
+      <c r="C147" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a bright yellow sun with squinting eyes and a bothered face, sunglasses sitting on top of its head forgotten, having little cute feet"</v>
+      </c>
       <c r="D147" t="str">
         <v>Nature</v>
       </c>
@@ -5744,6 +5939,9 @@
       <c r="B148" t="str">
         <v>Thunder is banging his drums way too loud again!</v>
       </c>
+      <c r="C148" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a rockstar-style dark grey thunder cloud with drumsticks, banging on tiny drums with an excited wild face"</v>
+      </c>
       <c r="D148" t="str">
         <v>Nature</v>
       </c>
@@ -5779,6 +5977,9 @@
       <c r="B149" t="str">
         <v>Wind is blowing out birthday candles that aren't even his!</v>
       </c>
+      <c r="C149" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a swirly light blue wind spirit with puffed cheeks blowing hard, a tiny birthday cake with candles going out"</v>
+      </c>
       <c r="D149" t="str">
         <v>Nature</v>
       </c>
@@ -5814,6 +6015,9 @@
       <c r="B150" t="str">
         <v>Eight is a snowman begging for warm hugs!</v>
       </c>
+      <c r="C150" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 8 dressed as a snowman with a tiny scarf and a top hat, both arms reaching out with a hopeful pleading face, having little cute feet"</v>
+      </c>
       <c r="D150" t="str">
         <v>Numbers</v>
       </c>
@@ -5821,7 +6025,7 @@
         <v>1</v>
       </c>
       <c r="F150" t="str">
-        <v>八</v>
+        <v>数字8</v>
       </c>
       <c r="G150" t="str">
         <v>bā</v>
@@ -5849,6 +6053,9 @@
       <c r="B151" t="str">
         <v>Five is a chubby little Santa with a big round belly!</v>
       </c>
+      <c r="C151" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 5 dressed as Santa with a red hat and white beard, its round bottom half looking like a big jolly tummy, having little cute feet"</v>
+      </c>
       <c r="D151" t="str">
         <v>Numbers</v>
       </c>
@@ -5856,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="F151" t="str">
-        <v>五</v>
+        <v>数字5</v>
       </c>
       <c r="G151" t="str">
         <v>wǔ</v>
@@ -5884,6 +6091,9 @@
       <c r="B152" t="str">
         <v>Four is a grumpy chair who hates being sat on!</v>
       </c>
+      <c r="C152" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 4 dressed as a wooden chair, with a grumpy annoyed face, tiny arms crossed"</v>
+      </c>
       <c r="D152" t="str">
         <v>Numbers</v>
       </c>
@@ -5891,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="F152" t="str">
-        <v>四</v>
+        <v>数字4</v>
       </c>
       <c r="G152" t="str">
         <v>sì</v>
@@ -5919,6 +6129,9 @@
       <c r="B153" t="str">
         <v>Nine is a smart professor with a giant brain.</v>
       </c>
+      <c r="C153" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 9 in professor-style with tiny glasses, its big round top looking like a giant brain, with a proud smart face"</v>
+      </c>
       <c r="D153" t="str">
         <v>Numbers</v>
       </c>
@@ -5926,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="F153" t="str">
-        <v>九</v>
+        <v>数字9</v>
       </c>
       <c r="G153" t="str">
         <v>jiǔ</v>
@@ -5954,6 +6167,9 @@
       <c r="B154" t="str">
         <v>One is a skinny pencil with a big eraser hat!</v>
       </c>
+      <c r="C154" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 1 dressed as a yellow pencil with a big pink eraser on top like a hat, with a cheerful face"</v>
+      </c>
       <c r="D154" t="str">
         <v>Numbers</v>
       </c>
@@ -5961,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="F154" t="str">
-        <v>一</v>
+        <v>数字1</v>
       </c>
       <c r="G154" t="str">
         <v>yī</v>
@@ -5989,6 +6205,9 @@
       <c r="B155" t="str">
         <v>Seven is a candy cane that never tastes like mint!</v>
       </c>
+      <c r="C155" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 7 dressed as a candy cane with red and white stripes, with a disappointed pouty face"</v>
+      </c>
       <c r="D155" t="str">
         <v>Numbers</v>
       </c>
@@ -5996,7 +6215,7 @@
         <v>1</v>
       </c>
       <c r="F155" t="str">
-        <v>七</v>
+        <v>数字7</v>
       </c>
       <c r="G155" t="str">
         <v>qī</v>
@@ -6024,6 +6243,9 @@
       <c r="B156" t="str">
         <v>Six is a little snail dragging her big round shell!</v>
       </c>
+      <c r="C156" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 6 dressed as a snail with tiny antennae, its round top looking like a big spiral shell, with a tired slow face"</v>
+      </c>
       <c r="D156" t="str">
         <v>Numbers</v>
       </c>
@@ -6031,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="F156" t="str">
-        <v>六</v>
+        <v>数字6</v>
       </c>
       <c r="G156" t="str">
         <v>liù</v>
@@ -6059,6 +6281,9 @@
       <c r="B157" t="str">
         <v>Ten is a baseball bat standing next to his fast little ball!</v>
       </c>
+      <c r="C157" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 1 dressed as a baseball bat with a sporty confident face, next to a number 0 dressed as a baseball with an excited face"</v>
+      </c>
       <c r="D157" t="str">
         <v>Numbers</v>
       </c>
@@ -6066,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="F157" t="str">
-        <v>十</v>
+        <v>数字10</v>
       </c>
       <c r="G157" t="str">
         <v>shí</v>
@@ -6094,6 +6319,9 @@
       <c r="B158" t="str">
         <v>Three is a chubby bumblebee too heavy to fly!</v>
       </c>
+      <c r="C158" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a chubby number 3 dressed as a bumblebee with tiny wings and yellow-black stripes, with a struggling exhausted face, having little cute feet"</v>
+      </c>
       <c r="D158" t="str">
         <v>Numbers</v>
       </c>
@@ -6101,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="F158" t="str">
-        <v>三</v>
+        <v>数字3</v>
       </c>
       <c r="G158" t="str">
         <v>sān</v>
@@ -6129,6 +6357,9 @@
       <c r="B159" t="str">
         <v>Two is a yellow ducky with a tiny orange beak!</v>
       </c>
+      <c r="C159" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 2 dressed as a yellow rubber ducky with a tiny orange beak, with a happy quacking face, having little cute feet"</v>
+      </c>
       <c r="D159" t="str">
         <v>Numbers</v>
       </c>
@@ -6136,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="F159" t="str">
-        <v>二</v>
+        <v>数字2</v>
       </c>
       <c r="G159" t="str">
         <v>èr</v>
@@ -6164,6 +6395,9 @@
       <c r="B160" t="str">
         <v>Zero is a giant donut with pink frosting on top!</v>
       </c>
+      <c r="C160" t="str">
+        <v>PlushStyle, plush style, white background, a super cute plush toy of "a number 0 dressed as a donut with pink frosting and colorful sprinkles, with a sweet happy face, having little cute feet"</v>
+      </c>
       <c r="D160" t="str">
         <v>Numbers</v>
       </c>
@@ -6171,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="F160" t="str">
-        <v>零</v>
+        <v>数字0</v>
       </c>
       <c r="G160" t="str">
         <v>líng</v>
@@ -6627,7 +6861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B15"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -6643,87 +6877,119 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>vocab-food</v>
+        <v>vocab-animal</v>
       </c>
       <c r="B2" t="str">
-        <v>beef</v>
+        <v>pig</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>vocab-animal</v>
+        <v>vocab-adjective</v>
       </c>
       <c r="B3" t="str">
-        <v>bird</v>
+        <v>good</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>vocab-body</v>
+        <v>vocab-food</v>
       </c>
       <c r="B4" t="str">
-        <v>hand</v>
+        <v>mushroom</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>vocab-clothes</v>
+        <v>vocab-places</v>
       </c>
       <c r="B5" t="str">
-        <v>hat</v>
+        <v>airport</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>vocab-colors</v>
+        <v>vocab-body</v>
       </c>
       <c r="B6" t="str">
-        <v>pink</v>
+        <v>eye</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>vocab-places</v>
+        <v>vocab-clothes</v>
       </c>
       <c r="B7" t="str">
-        <v>bank</v>
+        <v>pants</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>oral-everyday</v>
+        <v>vocab-colors</v>
       </c>
       <c r="B8" t="str">
-        <v>cake</v>
+        <v>blue</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>oral-food</v>
+        <v>vocab-items</v>
       </c>
       <c r="B9" t="str">
-        <v>beef</v>
+        <v>computer</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>oral-emotions</v>
+        <v>vocab-nature</v>
       </c>
       <c r="B10" t="str">
-        <v>bear</v>
+        <v>rain</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>vocab-numbers</v>
+      </c>
+      <c r="B11" t="str">
+        <v>eight</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>oral-everyday</v>
+      </c>
+      <c r="B12" t="str">
+        <v>orange</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
         <v>oral-opinions</v>
       </c>
-      <c r="B11" t="str">
-        <v>elephant</v>
+      <c r="B13" t="str">
+        <v>cherry</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>oral-food</v>
+      </c>
+      <c r="B14" t="str">
+        <v>hungry</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>oral-emotions</v>
+      </c>
+      <c r="B15" t="str">
+        <v>durian</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/update_data_folder/WordList.xlsx
+++ b/update_data_folder/WordList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miaofang/Desktop/VocabWorkspace/update_data_folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE55C7D9-5C83-184D-BE76-D22F4840D8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8AA265-DE00-E745-8778-C2C985D60CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="920" windowWidth="32820" windowHeight="21420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="800" yWindow="10040" windowWidth="32820" windowHeight="21420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="单词" sheetId="1" r:id="rId1"/>
@@ -4697,9 +4697,6 @@
     <t>qī</t>
   </si>
   <si>
-    <t>七是一根拐杖糖，但从里到外都不是薄荷味！</t>
-  </si>
-  <si>
     <t>&lt;ruby&gt;七&lt;rt&gt;なな&lt;/rt&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -4847,9 +4844,6 @@
     <t>líng</t>
   </si>
   <si>
-    <t>零是一个大大的甜甜圈，上面还淋着粉粉的糖霜！</t>
-  </si>
-  <si>
     <t>ゼロ</t>
   </si>
   <si>
@@ -4877,9 +4871,6 @@
     <t>gēge</t>
   </si>
   <si>
-    <t>哥哥房间乱糟糟的，他却赖到小狗头上！</t>
-  </si>
-  <si>
     <t>お&lt;ruby&gt;兄&lt;rt&gt;にい&lt;/rt&gt;&lt;/ruby&gt;ちゃん</t>
   </si>
   <si>
@@ -4937,9 +4928,6 @@
     <t>péngyou</t>
   </si>
   <si>
-    <t>朋友把巧克力大一点的那半留给你啦</t>
-  </si>
-  <si>
     <t>&lt;ruby&gt;友達&lt;rt&gt;ともだち&lt;/rt&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -8937,6 +8925,18 @@
   </si>
   <si>
     <t>面包窝在暖烘烘的烤面包机里，睡得正香。</t>
+  </si>
+  <si>
+    <t>哥哥自己把房间弄得乱糟糟，却赖到小狗头上！</t>
+  </si>
+  <si>
+    <t>七是一根拐杖糖，可怎么尝都不是薄荷味！</t>
+  </si>
+  <si>
+    <t>零是一个大大的甜甜圈，顶上还淋着粉粉的糖霜！</t>
+  </si>
+  <si>
+    <t>朋友把巧克力大一点的那半留给你啦！</t>
   </si>
 </sst>
 </file>
@@ -12152,7 +12152,7 @@
         <v>697</v>
       </c>
       <c r="J70" t="s">
-        <v>2971</v>
+        <v>2967</v>
       </c>
       <c r="K70" t="s">
         <v>698</v>
@@ -15382,27 +15382,27 @@
         <v>1557</v>
       </c>
       <c r="J155" t="s">
+        <v>2969</v>
+      </c>
+      <c r="K155" t="s">
         <v>1558</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" s="10" t="s">
         <v>1559</v>
       </c>
-      <c r="L155" s="10" t="s">
+      <c r="M155" t="s">
         <v>1560</v>
-      </c>
-      <c r="M155" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>1562</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
         <v>1563</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>1564</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>1504</v>
@@ -15411,36 +15411,36 @@
         <v>1504</v>
       </c>
       <c r="G156" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="H156" s="10" t="s">
         <v>1565</v>
       </c>
-      <c r="H156" s="10" t="s">
+      <c r="I156" t="s">
         <v>1566</v>
       </c>
-      <c r="I156" t="s">
+      <c r="J156" s="10" t="s">
         <v>1567</v>
       </c>
-      <c r="J156" s="10" t="s">
+      <c r="K156" t="s">
         <v>1568</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" s="10" t="s">
         <v>1569</v>
       </c>
-      <c r="L156" s="10" t="s">
+      <c r="M156" t="s">
         <v>1570</v>
-      </c>
-      <c r="M156" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>1572</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
         <v>1573</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>1574</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>1504</v>
@@ -15449,36 +15449,36 @@
         <v>1504</v>
       </c>
       <c r="G157" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="H157" s="10" t="s">
         <v>1575</v>
       </c>
-      <c r="H157" s="10" t="s">
+      <c r="I157" t="s">
         <v>1576</v>
       </c>
-      <c r="I157" t="s">
+      <c r="J157" s="15" t="s">
         <v>1577</v>
       </c>
-      <c r="J157" s="15" t="s">
+      <c r="K157" t="s">
         <v>1578</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" s="10" t="s">
         <v>1579</v>
       </c>
-      <c r="L157" s="10" t="s">
+      <c r="M157" t="s">
         <v>1580</v>
-      </c>
-      <c r="M157" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>1582</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
         <v>1583</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>1584</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>1504</v>
@@ -15487,36 +15487,36 @@
         <v>1504</v>
       </c>
       <c r="G158" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H158" s="10" t="s">
         <v>1585</v>
       </c>
-      <c r="H158" s="10" t="s">
+      <c r="I158" t="s">
         <v>1586</v>
       </c>
-      <c r="I158" t="s">
+      <c r="J158" t="s">
         <v>1587</v>
       </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>1588</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" s="10" t="s">
         <v>1589</v>
       </c>
-      <c r="L158" s="10" t="s">
+      <c r="M158" s="8" t="s">
         <v>1590</v>
-      </c>
-      <c r="M158" s="8" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>1592</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="C159" s="1" t="s">
         <v>1593</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>1594</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>1504</v>
@@ -15525,36 +15525,36 @@
         <v>1504</v>
       </c>
       <c r="G159" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="H159" s="10" t="s">
         <v>1595</v>
       </c>
-      <c r="H159" s="10" t="s">
+      <c r="I159" t="s">
         <v>1596</v>
       </c>
-      <c r="I159" t="s">
+      <c r="J159" s="15" t="s">
         <v>1597</v>
       </c>
-      <c r="J159" s="15" t="s">
+      <c r="K159" t="s">
         <v>1598</v>
       </c>
-      <c r="K159" t="s">
+      <c r="L159" s="10" t="s">
         <v>1599</v>
       </c>
-      <c r="L159" s="10" t="s">
+      <c r="M159" t="s">
         <v>1600</v>
-      </c>
-      <c r="M159" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>1602</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
         <v>1603</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>1604</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>1504</v>
@@ -15563,378 +15563,378 @@
         <v>1504</v>
       </c>
       <c r="G160" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H160" s="10" t="s">
         <v>1605</v>
       </c>
-      <c r="H160" s="10" t="s">
+      <c r="I160" t="s">
         <v>1606</v>
       </c>
-      <c r="I160" t="s">
+      <c r="J160" t="s">
+        <v>2970</v>
+      </c>
+      <c r="K160" t="s">
         <v>1607</v>
       </c>
-      <c r="J160" t="s">
+      <c r="L160" s="10" t="s">
+        <v>1601</v>
+      </c>
+      <c r="M160" t="s">
         <v>1608</v>
-      </c>
-      <c r="K160" t="s">
-        <v>1609</v>
-      </c>
-      <c r="L160" s="10" t="s">
-        <v>1602</v>
-      </c>
-      <c r="M160" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>1611</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>1612</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>1613</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F161" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>1613</v>
+      </c>
+      <c r="H161" s="4" t="s">
         <v>1614</v>
       </c>
-      <c r="G161" s="1" t="s">
+      <c r="I161" s="4" t="s">
         <v>1615</v>
       </c>
-      <c r="H161" s="4" t="s">
+      <c r="J161" s="10" t="s">
+        <v>2968</v>
+      </c>
+      <c r="K161" t="s">
         <v>1616</v>
       </c>
-      <c r="I161" s="4" t="s">
+      <c r="L161" s="10" t="s">
         <v>1617</v>
       </c>
-      <c r="J161" s="10" t="s">
+      <c r="M161" s="8" t="s">
         <v>1618</v>
-      </c>
-      <c r="K161" t="s">
-        <v>1619</v>
-      </c>
-      <c r="L161" s="10" t="s">
-        <v>1620</v>
-      </c>
-      <c r="M161" s="8" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G162" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H162" s="10" t="s">
+        <v>1623</v>
+      </c>
+      <c r="I162" t="s">
+        <v>1624</v>
+      </c>
+      <c r="J162" s="10" t="s">
         <v>1625</v>
       </c>
-      <c r="H162" s="10" t="s">
+      <c r="K162" t="s">
         <v>1626</v>
       </c>
-      <c r="I162" t="s">
+      <c r="L162" s="10" t="s">
         <v>1627</v>
       </c>
-      <c r="J162" s="10" t="s">
+      <c r="M162" s="8" t="s">
         <v>1628</v>
-      </c>
-      <c r="K162" t="s">
-        <v>1629</v>
-      </c>
-      <c r="L162" s="10" t="s">
-        <v>1630</v>
-      </c>
-      <c r="M162" s="8" t="s">
-        <v>1631</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G163" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="H163" s="10" t="s">
+        <v>1633</v>
+      </c>
+      <c r="I163" t="s">
+        <v>1634</v>
+      </c>
+      <c r="J163" s="15" t="s">
+        <v>2971</v>
+      </c>
+      <c r="K163" t="s">
         <v>1635</v>
       </c>
-      <c r="H163" s="10" t="s">
+      <c r="L163" s="10" t="s">
         <v>1636</v>
       </c>
-      <c r="I163" t="s">
+      <c r="M163" s="8" t="s">
         <v>1637</v>
-      </c>
-      <c r="J163" s="15" t="s">
-        <v>1638</v>
-      </c>
-      <c r="K163" t="s">
-        <v>1639</v>
-      </c>
-      <c r="L163" s="10" t="s">
-        <v>1640</v>
-      </c>
-      <c r="M163" s="8" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>1643</v>
+        <v>1639</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G164" s="1" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H164" s="10" t="s">
+        <v>1642</v>
+      </c>
+      <c r="I164" t="s">
+        <v>1643</v>
+      </c>
+      <c r="J164" s="10" t="s">
+        <v>1644</v>
+      </c>
+      <c r="K164" t="s">
         <v>1645</v>
       </c>
-      <c r="H164" s="10" t="s">
+      <c r="L164" s="10" t="s">
         <v>1646</v>
       </c>
-      <c r="I164" t="s">
+      <c r="M164" s="8" t="s">
         <v>1647</v>
-      </c>
-      <c r="J164" s="10" t="s">
-        <v>1648</v>
-      </c>
-      <c r="K164" t="s">
-        <v>1649</v>
-      </c>
-      <c r="L164" s="10" t="s">
-        <v>1650</v>
-      </c>
-      <c r="M164" s="8" t="s">
-        <v>1651</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>1652</v>
+        <v>1648</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>1653</v>
+        <v>1649</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G165" s="1" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H165" s="10" t="s">
+        <v>1652</v>
+      </c>
+      <c r="I165" t="s">
+        <v>1653</v>
+      </c>
+      <c r="J165" s="10" t="s">
+        <v>1654</v>
+      </c>
+      <c r="K165" t="s">
         <v>1655</v>
       </c>
-      <c r="H165" s="10" t="s">
+      <c r="L165" s="10" t="s">
         <v>1656</v>
       </c>
-      <c r="I165" t="s">
+      <c r="M165" s="8" t="s">
         <v>1657</v>
-      </c>
-      <c r="J165" s="10" t="s">
-        <v>1658</v>
-      </c>
-      <c r="K165" t="s">
-        <v>1659</v>
-      </c>
-      <c r="L165" s="10" t="s">
-        <v>1660</v>
-      </c>
-      <c r="M165" s="8" t="s">
-        <v>1661</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G166" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H166" s="10" t="s">
+        <v>1662</v>
+      </c>
+      <c r="I166" t="s">
+        <v>1663</v>
+      </c>
+      <c r="J166" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K166" t="s">
         <v>1665</v>
       </c>
-      <c r="H166" s="10" t="s">
+      <c r="L166" s="10" t="s">
         <v>1666</v>
       </c>
-      <c r="I166" t="s">
+      <c r="M166" s="8" t="s">
         <v>1667</v>
-      </c>
-      <c r="J166" t="s">
-        <v>1668</v>
-      </c>
-      <c r="K166" t="s">
-        <v>1669</v>
-      </c>
-      <c r="L166" s="10" t="s">
-        <v>1670</v>
-      </c>
-      <c r="M166" s="8" t="s">
-        <v>1671</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="G167" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="I167" t="s">
+        <v>1673</v>
+      </c>
+      <c r="J167" t="s">
+        <v>1674</v>
+      </c>
+      <c r="K167" t="s">
         <v>1675</v>
       </c>
-      <c r="H167" s="1" t="s">
+      <c r="L167" s="10" t="s">
         <v>1676</v>
       </c>
-      <c r="I167" t="s">
+      <c r="M167" s="8" t="s">
         <v>1677</v>
-      </c>
-      <c r="J167" t="s">
-        <v>1678</v>
-      </c>
-      <c r="K167" t="s">
-        <v>1679</v>
-      </c>
-      <c r="L167" s="10" t="s">
-        <v>1680</v>
-      </c>
-      <c r="M167" s="8" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>1683</v>
+        <v>1679</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>1684</v>
+        <v>1680</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F168" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>1683</v>
+      </c>
+      <c r="I168" t="s">
+        <v>1684</v>
+      </c>
+      <c r="J168" t="s">
         <v>1685</v>
       </c>
-      <c r="G168" s="1" t="s">
+      <c r="K168" t="s">
         <v>1686</v>
       </c>
-      <c r="H168" s="10" t="s">
+      <c r="L168" s="10" t="s">
         <v>1687</v>
       </c>
-      <c r="I168" t="s">
+      <c r="M168" s="8" t="s">
         <v>1688</v>
-      </c>
-      <c r="J168" t="s">
-        <v>1689</v>
-      </c>
-      <c r="K168" t="s">
-        <v>1690</v>
-      </c>
-      <c r="L168" s="10" t="s">
-        <v>1691</v>
-      </c>
-      <c r="M168" s="8" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>1693</v>
+        <v>1689</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>1695</v>
+        <v>1691</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F169" s="1" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>1693</v>
+      </c>
+      <c r="H169" s="10" t="s">
+        <v>1694</v>
+      </c>
+      <c r="I169" t="s">
+        <v>1695</v>
+      </c>
+      <c r="J169" s="11" t="s">
         <v>1696</v>
       </c>
-      <c r="G169" s="1" t="s">
+      <c r="K169" t="s">
         <v>1697</v>
       </c>
-      <c r="H169" s="10" t="s">
+      <c r="L169" s="10" t="s">
         <v>1698</v>
       </c>
-      <c r="I169" t="s">
+      <c r="M169" s="8" t="s">
         <v>1699</v>
-      </c>
-      <c r="J169" s="11" t="s">
-        <v>1700</v>
-      </c>
-      <c r="K169" t="s">
-        <v>1701</v>
-      </c>
-      <c r="L169" s="10" t="s">
-        <v>1702</v>
-      </c>
-      <c r="M169" s="8" t="s">
-        <v>1703</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>1704</v>
+        <v>1700</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>240</v>
@@ -15943,36 +15943,36 @@
         <v>240</v>
       </c>
       <c r="G170" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>1704</v>
+      </c>
+      <c r="I170" t="s">
+        <v>1705</v>
+      </c>
+      <c r="J170" s="10" t="s">
+        <v>1706</v>
+      </c>
+      <c r="K170" t="s">
         <v>1707</v>
       </c>
-      <c r="H170" s="10" t="s">
+      <c r="L170" s="10" t="s">
         <v>1708</v>
       </c>
-      <c r="I170" t="s">
+      <c r="M170" s="8" t="s">
         <v>1709</v>
-      </c>
-      <c r="J170" s="10" t="s">
-        <v>1710</v>
-      </c>
-      <c r="K170" t="s">
-        <v>1711</v>
-      </c>
-      <c r="L170" s="10" t="s">
-        <v>1712</v>
-      </c>
-      <c r="M170" s="8" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>1714</v>
+        <v>1710</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>240</v>
@@ -15981,36 +15981,36 @@
         <v>240</v>
       </c>
       <c r="G171" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="H171" s="10" t="s">
+        <v>1714</v>
+      </c>
+      <c r="I171" t="s">
+        <v>1715</v>
+      </c>
+      <c r="J171" s="10" t="s">
+        <v>1716</v>
+      </c>
+      <c r="K171" t="s">
         <v>1717</v>
       </c>
-      <c r="H171" s="10" t="s">
+      <c r="L171" s="10" t="s">
         <v>1718</v>
       </c>
-      <c r="I171" t="s">
+      <c r="M171" t="s">
         <v>1719</v>
-      </c>
-      <c r="J171" s="10" t="s">
-        <v>1720</v>
-      </c>
-      <c r="K171" t="s">
-        <v>1721</v>
-      </c>
-      <c r="L171" s="10" t="s">
-        <v>1722</v>
-      </c>
-      <c r="M171" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>1724</v>
+        <v>1720</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>1725</v>
+        <v>1721</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1726</v>
+        <v>1722</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>240</v>
@@ -16019,36 +16019,36 @@
         <v>240</v>
       </c>
       <c r="G172" s="1" t="s">
+        <v>1723</v>
+      </c>
+      <c r="H172" s="10" t="s">
+        <v>1724</v>
+      </c>
+      <c r="I172" t="s">
+        <v>1725</v>
+      </c>
+      <c r="J172" s="10" t="s">
+        <v>1726</v>
+      </c>
+      <c r="K172" t="s">
         <v>1727</v>
       </c>
-      <c r="H172" s="10" t="s">
+      <c r="L172" s="10" t="s">
         <v>1728</v>
       </c>
-      <c r="I172" t="s">
+      <c r="M172" t="s">
         <v>1729</v>
-      </c>
-      <c r="J172" s="10" t="s">
-        <v>1730</v>
-      </c>
-      <c r="K172" t="s">
-        <v>1731</v>
-      </c>
-      <c r="L172" s="10" t="s">
-        <v>1732</v>
-      </c>
-      <c r="M172" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>1734</v>
+        <v>1730</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>1735</v>
+        <v>1731</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1736</v>
+        <v>1732</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>240</v>
@@ -16057,150 +16057,150 @@
         <v>240</v>
       </c>
       <c r="G173" s="1" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H173" s="10" t="s">
+        <v>1734</v>
+      </c>
+      <c r="I173" t="s">
+        <v>1735</v>
+      </c>
+      <c r="J173" s="10" t="s">
+        <v>1736</v>
+      </c>
+      <c r="K173" t="s">
         <v>1737</v>
       </c>
-      <c r="H173" s="10" t="s">
+      <c r="L173" s="10" t="s">
         <v>1738</v>
       </c>
-      <c r="I173" t="s">
+      <c r="M173" t="s">
         <v>1739</v>
-      </c>
-      <c r="J173" s="10" t="s">
-        <v>1740</v>
-      </c>
-      <c r="K173" t="s">
-        <v>1741</v>
-      </c>
-      <c r="L173" s="10" t="s">
-        <v>1742</v>
-      </c>
-      <c r="M173" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>1744</v>
+        <v>1740</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>1745</v>
+        <v>1741</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>1746</v>
+        <v>1742</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F174" s="1" t="s">
+        <v>1743</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="H174" s="10" t="s">
+        <v>1745</v>
+      </c>
+      <c r="I174" t="s">
+        <v>1746</v>
+      </c>
+      <c r="J174" t="s">
         <v>1747</v>
       </c>
-      <c r="G174" s="1" t="s">
+      <c r="K174" t="s">
         <v>1748</v>
       </c>
-      <c r="H174" s="10" t="s">
+      <c r="L174" s="10" t="s">
         <v>1749</v>
       </c>
-      <c r="I174" t="s">
+      <c r="M174" t="s">
         <v>1750</v>
-      </c>
-      <c r="J174" t="s">
-        <v>1751</v>
-      </c>
-      <c r="K174" t="s">
-        <v>1752</v>
-      </c>
-      <c r="L174" s="10" t="s">
-        <v>1753</v>
-      </c>
-      <c r="M174" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>1755</v>
+        <v>1751</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>1757</v>
+        <v>1753</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
       <c r="G175" s="1" t="s">
+        <v>1754</v>
+      </c>
+      <c r="H175" s="10" t="s">
+        <v>1755</v>
+      </c>
+      <c r="I175" s="23" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J175" t="s">
+        <v>1757</v>
+      </c>
+      <c r="K175" t="s">
         <v>1758</v>
       </c>
-      <c r="H175" s="10" t="s">
+      <c r="L175" s="10" t="s">
         <v>1759</v>
       </c>
-      <c r="I175" s="23" t="s">
+      <c r="M175" s="7" t="s">
         <v>1760</v>
-      </c>
-      <c r="J175" t="s">
-        <v>1761</v>
-      </c>
-      <c r="K175" t="s">
-        <v>1762</v>
-      </c>
-      <c r="L175" s="10" t="s">
-        <v>1763</v>
-      </c>
-      <c r="M175" s="7" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>1766</v>
+        <v>1762</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>1767</v>
+        <v>1763</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
       <c r="G176" s="1" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H176" s="10" t="s">
+        <v>1765</v>
+      </c>
+      <c r="I176" t="s">
+        <v>1766</v>
+      </c>
+      <c r="J176" s="10" t="s">
+        <v>1767</v>
+      </c>
+      <c r="K176" t="s">
         <v>1768</v>
-      </c>
-      <c r="H176" s="10" t="s">
-        <v>1769</v>
-      </c>
-      <c r="I176" t="s">
-        <v>1770</v>
-      </c>
-      <c r="J176" s="10" t="s">
-        <v>1771</v>
-      </c>
-      <c r="K176" t="s">
-        <v>1772</v>
       </c>
       <c r="L176" s="10" t="s">
         <v>316</v>
       </c>
       <c r="M176" t="s">
-        <v>1773</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>1774</v>
+        <v>1770</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>1775</v>
+        <v>1771</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>1776</v>
+        <v>1772</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>240</v>
@@ -16209,36 +16209,36 @@
         <v>240</v>
       </c>
       <c r="G177" s="1" t="s">
+        <v>1773</v>
+      </c>
+      <c r="H177" s="10" t="s">
+        <v>1774</v>
+      </c>
+      <c r="I177" t="s">
+        <v>1775</v>
+      </c>
+      <c r="J177" t="s">
+        <v>1776</v>
+      </c>
+      <c r="K177" t="s">
         <v>1777</v>
       </c>
-      <c r="H177" s="10" t="s">
+      <c r="L177" s="10" t="s">
         <v>1778</v>
       </c>
-      <c r="I177" t="s">
+      <c r="M177" t="s">
         <v>1779</v>
-      </c>
-      <c r="J177" t="s">
-        <v>1780</v>
-      </c>
-      <c r="K177" t="s">
-        <v>1781</v>
-      </c>
-      <c r="L177" s="10" t="s">
-        <v>1782</v>
-      </c>
-      <c r="M177" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>1784</v>
+        <v>1780</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>1785</v>
+        <v>1781</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>966</v>
@@ -16247,1898 +16247,1898 @@
         <v>978</v>
       </c>
       <c r="G178" s="1" t="s">
+        <v>1783</v>
+      </c>
+      <c r="H178" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>1785</v>
+      </c>
+      <c r="J178" t="s">
+        <v>1786</v>
+      </c>
+      <c r="K178" t="s">
         <v>1787</v>
       </c>
-      <c r="H178" s="7" t="s">
+      <c r="L178" s="10" t="s">
         <v>1788</v>
       </c>
-      <c r="I178" s="4" t="s">
+      <c r="M178" s="7" t="s">
         <v>1789</v>
-      </c>
-      <c r="J178" t="s">
-        <v>1790</v>
-      </c>
-      <c r="K178" t="s">
-        <v>1791</v>
-      </c>
-      <c r="L178" s="10" t="s">
-        <v>1792</v>
-      </c>
-      <c r="M178" s="7" t="s">
-        <v>1793</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>1794</v>
+        <v>1790</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>1795</v>
+        <v>1791</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1796</v>
+        <v>1792</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F179" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="H179" s="10" t="s">
+        <v>1795</v>
+      </c>
+      <c r="I179" t="s">
+        <v>1796</v>
+      </c>
+      <c r="J179" t="s">
         <v>1797</v>
       </c>
-      <c r="G179" s="1" t="s">
+      <c r="K179" t="s">
         <v>1798</v>
       </c>
-      <c r="H179" s="10" t="s">
+      <c r="L179" s="10" t="s">
         <v>1799</v>
       </c>
-      <c r="I179" t="s">
+      <c r="M179" t="s">
         <v>1800</v>
-      </c>
-      <c r="J179" t="s">
-        <v>1801</v>
-      </c>
-      <c r="K179" t="s">
-        <v>1802</v>
-      </c>
-      <c r="L179" s="10" t="s">
-        <v>1803</v>
-      </c>
-      <c r="M179" t="s">
-        <v>1804</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F180" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>1805</v>
+      </c>
+      <c r="H180" s="10" t="s">
+        <v>1806</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>1807</v>
+      </c>
+      <c r="J180" s="17" t="s">
         <v>1808</v>
       </c>
-      <c r="G180" s="1" t="s">
+      <c r="K180" t="s">
         <v>1809</v>
       </c>
-      <c r="H180" s="10" t="s">
+      <c r="L180" s="10" t="s">
         <v>1810</v>
       </c>
-      <c r="I180" s="4" t="s">
+      <c r="M180" t="s">
         <v>1811</v>
-      </c>
-      <c r="J180" s="17" t="s">
-        <v>1812</v>
-      </c>
-      <c r="K180" t="s">
-        <v>1813</v>
-      </c>
-      <c r="L180" s="10" t="s">
-        <v>1814</v>
-      </c>
-      <c r="M180" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>1816</v>
+        <v>1812</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>1817</v>
+        <v>1813</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>1818</v>
+        <v>1814</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="G181" s="1" t="s">
+        <v>1815</v>
+      </c>
+      <c r="H181" s="10" t="s">
+        <v>1816</v>
+      </c>
+      <c r="I181" t="s">
+        <v>1817</v>
+      </c>
+      <c r="J181" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K181" t="s">
         <v>1819</v>
       </c>
-      <c r="H181" s="10" t="s">
+      <c r="L181" s="10" t="s">
         <v>1820</v>
       </c>
-      <c r="I181" t="s">
+      <c r="M181" t="s">
         <v>1821</v>
-      </c>
-      <c r="J181" t="s">
-        <v>1822</v>
-      </c>
-      <c r="K181" t="s">
-        <v>1823</v>
-      </c>
-      <c r="L181" s="10" t="s">
-        <v>1824</v>
-      </c>
-      <c r="M181" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>1826</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="G182" s="1" t="s">
         <v>1827</v>
       </c>
-      <c r="C182" s="1" t="s">
+      <c r="H182" s="10" t="s">
         <v>1828</v>
       </c>
-      <c r="E182" s="1" t="s">
+      <c r="I182" t="s">
         <v>1829</v>
       </c>
-      <c r="F182" s="1" t="s">
+      <c r="J182" t="s">
         <v>1830</v>
       </c>
-      <c r="G182" s="1" t="s">
+      <c r="K182" t="s">
         <v>1831</v>
       </c>
-      <c r="H182" s="10" t="s">
+      <c r="L182" s="10" t="s">
         <v>1832</v>
       </c>
-      <c r="I182" t="s">
+      <c r="M182" t="s">
         <v>1833</v>
-      </c>
-      <c r="J182" t="s">
-        <v>1834</v>
-      </c>
-      <c r="K182" t="s">
-        <v>1835</v>
-      </c>
-      <c r="L182" s="10" t="s">
-        <v>1836</v>
-      </c>
-      <c r="M182" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>1836</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="H183" s="10" t="s">
         <v>1838</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="I183" t="s">
         <v>1839</v>
       </c>
-      <c r="C183" s="1" t="s">
+      <c r="J183" s="10" t="s">
         <v>1840</v>
       </c>
-      <c r="E183" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G183" s="2" t="s">
+      <c r="K183" t="s">
         <v>1841</v>
       </c>
-      <c r="H183" s="10" t="s">
+      <c r="L183" s="10" t="s">
         <v>1842</v>
       </c>
-      <c r="I183" t="s">
+      <c r="M183" t="s">
         <v>1843</v>
-      </c>
-      <c r="J183" s="10" t="s">
-        <v>1844</v>
-      </c>
-      <c r="K183" t="s">
-        <v>1845</v>
-      </c>
-      <c r="L183" s="10" t="s">
-        <v>1846</v>
-      </c>
-      <c r="M183" t="s">
-        <v>1847</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>1847</v>
+      </c>
+      <c r="H184" s="10" t="s">
         <v>1848</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="I184" t="s">
         <v>1849</v>
       </c>
-      <c r="C184" s="1" t="s">
+      <c r="J184" t="s">
         <v>1850</v>
       </c>
-      <c r="E184" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G184" s="1" t="s">
+      <c r="K184" t="s">
         <v>1851</v>
       </c>
-      <c r="H184" s="10" t="s">
+      <c r="L184" s="10" t="s">
         <v>1852</v>
       </c>
-      <c r="I184" t="s">
+      <c r="M184" t="s">
         <v>1853</v>
-      </c>
-      <c r="J184" t="s">
-        <v>1854</v>
-      </c>
-      <c r="K184" t="s">
-        <v>1855</v>
-      </c>
-      <c r="L184" s="10" t="s">
-        <v>1856</v>
-      </c>
-      <c r="M184" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>1857</v>
+      </c>
+      <c r="H185" s="10" t="s">
         <v>1858</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="I185" t="s">
         <v>1859</v>
       </c>
-      <c r="C185" s="1" t="s">
+      <c r="J185" t="s">
         <v>1860</v>
       </c>
-      <c r="E185" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G185" s="1" t="s">
+      <c r="K185" t="s">
         <v>1861</v>
       </c>
-      <c r="H185" s="10" t="s">
+      <c r="L185" s="10" t="s">
         <v>1862</v>
       </c>
-      <c r="I185" t="s">
+      <c r="M185" s="8" t="s">
         <v>1863</v>
-      </c>
-      <c r="J185" t="s">
-        <v>1864</v>
-      </c>
-      <c r="K185" t="s">
-        <v>1865</v>
-      </c>
-      <c r="L185" s="10" t="s">
-        <v>1866</v>
-      </c>
-      <c r="M185" s="8" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F186" s="1" t="s">
         <v>1868</v>
       </c>
-      <c r="B186" s="1" t="s">
+      <c r="G186" s="1" t="s">
         <v>1869</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="H186" s="10" t="s">
         <v>1870</v>
       </c>
-      <c r="E186" s="1" t="s">
+      <c r="I186" t="s">
         <v>1871</v>
       </c>
-      <c r="F186" s="1" t="s">
+      <c r="J186" t="s">
         <v>1872</v>
       </c>
-      <c r="G186" s="1" t="s">
+      <c r="K186" t="s">
         <v>1873</v>
       </c>
-      <c r="H186" s="10" t="s">
+      <c r="L186" s="10" t="s">
         <v>1874</v>
       </c>
-      <c r="I186" t="s">
+      <c r="M186" t="s">
         <v>1875</v>
-      </c>
-      <c r="J186" t="s">
-        <v>1876</v>
-      </c>
-      <c r="K186" t="s">
-        <v>1877</v>
-      </c>
-      <c r="L186" s="10" t="s">
-        <v>1878</v>
-      </c>
-      <c r="M186" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>1878</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H187" s="10" t="s">
         <v>1880</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="I187" t="s">
         <v>1881</v>
       </c>
-      <c r="C187" s="1" t="s">
+      <c r="J187" s="10" t="s">
         <v>1882</v>
       </c>
-      <c r="E187" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="G187" s="1" t="s">
+      <c r="K187" t="s">
         <v>1883</v>
       </c>
-      <c r="H187" s="10" t="s">
+      <c r="L187" s="10" t="s">
         <v>1884</v>
       </c>
-      <c r="I187" t="s">
+      <c r="M187" t="s">
         <v>1885</v>
-      </c>
-      <c r="J187" s="10" t="s">
-        <v>1886</v>
-      </c>
-      <c r="K187" t="s">
-        <v>1887</v>
-      </c>
-      <c r="L187" s="10" t="s">
-        <v>1888</v>
-      </c>
-      <c r="M187" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>1889</v>
+      </c>
+      <c r="H188" s="1" t="s">
         <v>1890</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="I188" s="10" t="s">
         <v>1891</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="J188" s="17" t="s">
         <v>1892</v>
       </c>
-      <c r="E188" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="G188" s="1" t="s">
+      <c r="K188" t="s">
         <v>1893</v>
       </c>
-      <c r="H188" s="1" t="s">
+      <c r="L188" s="10" t="s">
         <v>1894</v>
       </c>
-      <c r="I188" s="10" t="s">
+      <c r="M188" t="s">
         <v>1895</v>
-      </c>
-      <c r="J188" s="17" t="s">
-        <v>1896</v>
-      </c>
-      <c r="K188" t="s">
-        <v>1897</v>
-      </c>
-      <c r="L188" s="10" t="s">
-        <v>1898</v>
-      </c>
-      <c r="M188" t="s">
-        <v>1899</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>1899</v>
+      </c>
+      <c r="H189" s="10" t="s">
         <v>1900</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="I189" t="s">
         <v>1901</v>
       </c>
-      <c r="C189" s="1" t="s">
+      <c r="J189" s="10" t="s">
         <v>1902</v>
       </c>
-      <c r="E189" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="G189" s="1" t="s">
+      <c r="K189" t="s">
         <v>1903</v>
       </c>
-      <c r="H189" s="10" t="s">
+      <c r="L189" s="10" t="s">
         <v>1904</v>
       </c>
-      <c r="I189" t="s">
+      <c r="M189" t="s">
         <v>1905</v>
-      </c>
-      <c r="J189" s="10" t="s">
-        <v>1906</v>
-      </c>
-      <c r="K189" t="s">
-        <v>1907</v>
-      </c>
-      <c r="L189" s="10" t="s">
-        <v>1908</v>
-      </c>
-      <c r="M189" t="s">
-        <v>1909</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>1908</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>1909</v>
+      </c>
+      <c r="H190" s="10" t="s">
         <v>1910</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="I190" t="s">
         <v>1911</v>
       </c>
-      <c r="C190" s="1" t="s">
+      <c r="J190" s="10" t="s">
         <v>1912</v>
       </c>
-      <c r="E190" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="G190" s="1" t="s">
+      <c r="K190" t="s">
         <v>1913</v>
       </c>
-      <c r="H190" s="10" t="s">
+      <c r="L190" s="10" t="s">
         <v>1914</v>
       </c>
-      <c r="I190" t="s">
+      <c r="M190" t="s">
         <v>1915</v>
-      </c>
-      <c r="J190" s="10" t="s">
-        <v>1916</v>
-      </c>
-      <c r="K190" t="s">
-        <v>1917</v>
-      </c>
-      <c r="L190" s="10" t="s">
-        <v>1918</v>
-      </c>
-      <c r="M190" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H191" s="10" t="s">
         <v>1920</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="I191" t="s">
         <v>1921</v>
       </c>
-      <c r="C191" s="1" t="s">
+      <c r="J191" s="10" t="s">
         <v>1922</v>
       </c>
-      <c r="E191" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="G191" s="1" t="s">
+      <c r="K191" t="s">
         <v>1923</v>
       </c>
-      <c r="H191" s="10" t="s">
+      <c r="L191" s="10" t="s">
         <v>1924</v>
       </c>
-      <c r="I191" t="s">
+      <c r="M191" t="s">
         <v>1925</v>
-      </c>
-      <c r="J191" s="10" t="s">
-        <v>1926</v>
-      </c>
-      <c r="K191" t="s">
-        <v>1927</v>
-      </c>
-      <c r="L191" s="10" t="s">
-        <v>1928</v>
-      </c>
-      <c r="M191" t="s">
-        <v>1929</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>1867</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>1929</v>
+      </c>
+      <c r="H192" s="10" t="s">
         <v>1930</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="I192" t="s">
         <v>1931</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="J192" t="s">
         <v>1932</v>
       </c>
-      <c r="E192" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>1871</v>
-      </c>
-      <c r="G192" s="1" t="s">
+      <c r="K192" t="s">
         <v>1933</v>
       </c>
-      <c r="H192" s="10" t="s">
+      <c r="L192" s="10" t="s">
         <v>1934</v>
       </c>
-      <c r="I192" t="s">
+      <c r="M192" t="s">
         <v>1935</v>
-      </c>
-      <c r="J192" t="s">
-        <v>1936</v>
-      </c>
-      <c r="K192" t="s">
-        <v>1937</v>
-      </c>
-      <c r="L192" s="10" t="s">
-        <v>1938</v>
-      </c>
-      <c r="M192" t="s">
-        <v>1939</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G193" s="1" t="s">
         <v>1940</v>
       </c>
-      <c r="B193" s="1" t="s">
+      <c r="H193" s="10" t="s">
         <v>1941</v>
       </c>
-      <c r="C193" s="1" t="s">
+      <c r="I193" t="s">
         <v>1942</v>
       </c>
-      <c r="E193" s="1" t="s">
+      <c r="J193" s="18" t="s">
         <v>1943</v>
       </c>
-      <c r="F193" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G193" s="1" t="s">
+      <c r="K193" t="s">
         <v>1944</v>
       </c>
-      <c r="H193" s="10" t="s">
+      <c r="L193" s="10" t="s">
         <v>1945</v>
       </c>
-      <c r="I193" t="s">
+      <c r="M193" t="s">
         <v>1946</v>
-      </c>
-      <c r="J193" s="18" t="s">
-        <v>1947</v>
-      </c>
-      <c r="K193" t="s">
-        <v>1948</v>
-      </c>
-      <c r="L193" s="10" t="s">
-        <v>1949</v>
-      </c>
-      <c r="M193" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>1950</v>
+      </c>
+      <c r="H194" s="10" t="s">
         <v>1951</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="I194" t="s">
         <v>1952</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="J194" t="s">
         <v>1953</v>
       </c>
-      <c r="E194" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G194" s="1" t="s">
+      <c r="K194" t="s">
         <v>1954</v>
       </c>
-      <c r="H194" s="10" t="s">
+      <c r="L194" s="10" t="s">
         <v>1955</v>
       </c>
-      <c r="I194" t="s">
+      <c r="M194" t="s">
         <v>1956</v>
-      </c>
-      <c r="J194" t="s">
-        <v>1957</v>
-      </c>
-      <c r="K194" t="s">
-        <v>1958</v>
-      </c>
-      <c r="L194" s="10" t="s">
-        <v>1959</v>
-      </c>
-      <c r="M194" t="s">
-        <v>1960</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>1960</v>
+      </c>
+      <c r="H195" s="10" t="s">
         <v>1961</v>
       </c>
-      <c r="B195" s="1" t="s">
+      <c r="I195" t="s">
         <v>1962</v>
       </c>
-      <c r="C195" s="1" t="s">
+      <c r="J195" s="18" t="s">
         <v>1963</v>
       </c>
-      <c r="E195" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G195" s="1" t="s">
+      <c r="K195" t="s">
         <v>1964</v>
       </c>
-      <c r="H195" s="10" t="s">
+      <c r="L195" s="10" t="s">
         <v>1965</v>
       </c>
-      <c r="I195" t="s">
+      <c r="M195" t="s">
         <v>1966</v>
-      </c>
-      <c r="J195" s="18" t="s">
-        <v>1967</v>
-      </c>
-      <c r="K195" t="s">
-        <v>1968</v>
-      </c>
-      <c r="L195" s="10" t="s">
-        <v>1969</v>
-      </c>
-      <c r="M195" t="s">
-        <v>1970</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>1970</v>
+      </c>
+      <c r="H196" s="10" t="s">
         <v>1971</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="I196" t="s">
         <v>1972</v>
       </c>
-      <c r="C196" s="1" t="s">
+      <c r="J196" s="18" t="s">
         <v>1973</v>
       </c>
-      <c r="E196" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G196" s="1" t="s">
+      <c r="K196" t="s">
         <v>1974</v>
       </c>
-      <c r="H196" s="10" t="s">
+      <c r="L196" s="10" t="s">
         <v>1975</v>
       </c>
-      <c r="I196" t="s">
+      <c r="M196" t="s">
         <v>1976</v>
-      </c>
-      <c r="J196" s="18" t="s">
-        <v>1977</v>
-      </c>
-      <c r="K196" t="s">
-        <v>1978</v>
-      </c>
-      <c r="L196" s="10" t="s">
-        <v>1979</v>
-      </c>
-      <c r="M196" t="s">
-        <v>1980</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H197" s="10" t="s">
         <v>1981</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="I197" t="s">
         <v>1982</v>
       </c>
-      <c r="C197" s="1" t="s">
+      <c r="J197" t="s">
         <v>1983</v>
       </c>
-      <c r="E197" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G197" s="1" t="s">
+      <c r="K197" t="s">
         <v>1984</v>
       </c>
-      <c r="H197" s="10" t="s">
+      <c r="L197" s="10" t="s">
         <v>1985</v>
       </c>
-      <c r="I197" t="s">
+      <c r="M197" t="s">
         <v>1986</v>
-      </c>
-      <c r="J197" t="s">
-        <v>1987</v>
-      </c>
-      <c r="K197" t="s">
-        <v>1988</v>
-      </c>
-      <c r="L197" s="10" t="s">
-        <v>1989</v>
-      </c>
-      <c r="M197" t="s">
-        <v>1990</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>1989</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="H198" s="10" t="s">
         <v>1991</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="I198" t="s">
         <v>1992</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="J198" t="s">
         <v>1993</v>
       </c>
-      <c r="E198" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G198" s="1" t="s">
+      <c r="K198" t="s">
         <v>1994</v>
       </c>
-      <c r="H198" s="10" t="s">
+      <c r="L198" s="10" t="s">
         <v>1995</v>
       </c>
-      <c r="I198" t="s">
+      <c r="M198" t="s">
         <v>1996</v>
-      </c>
-      <c r="J198" t="s">
-        <v>1997</v>
-      </c>
-      <c r="K198" t="s">
-        <v>1998</v>
-      </c>
-      <c r="L198" s="10" t="s">
-        <v>1999</v>
-      </c>
-      <c r="M198" t="s">
-        <v>2000</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>2000</v>
+      </c>
+      <c r="H199" s="10" t="s">
         <v>2001</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="I199" t="s">
         <v>2002</v>
       </c>
-      <c r="C199" s="1" t="s">
+      <c r="J199" t="s">
         <v>2003</v>
       </c>
-      <c r="E199" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G199" s="1" t="s">
+      <c r="K199" t="s">
         <v>2004</v>
       </c>
-      <c r="H199" s="10" t="s">
+      <c r="L199" s="10" t="s">
         <v>2005</v>
       </c>
-      <c r="I199" t="s">
+      <c r="M199" s="22" t="s">
         <v>2006</v>
-      </c>
-      <c r="J199" t="s">
-        <v>2007</v>
-      </c>
-      <c r="K199" t="s">
-        <v>2008</v>
-      </c>
-      <c r="L199" s="10" t="s">
-        <v>2009</v>
-      </c>
-      <c r="M199" s="22" t="s">
-        <v>2010</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>2009</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>2010</v>
+      </c>
+      <c r="H200" s="10" t="s">
         <v>2011</v>
       </c>
-      <c r="B200" s="1" t="s">
+      <c r="I200" t="s">
         <v>2012</v>
       </c>
-      <c r="C200" s="1" t="s">
+      <c r="J200" t="s">
         <v>2013</v>
       </c>
-      <c r="E200" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G200" s="1" t="s">
+      <c r="K200" t="s">
         <v>2014</v>
       </c>
-      <c r="H200" s="10" t="s">
+      <c r="L200" s="10" t="s">
         <v>2015</v>
       </c>
-      <c r="I200" t="s">
+      <c r="M200" t="s">
         <v>2016</v>
-      </c>
-      <c r="J200" t="s">
-        <v>2017</v>
-      </c>
-      <c r="K200" t="s">
-        <v>2018</v>
-      </c>
-      <c r="L200" s="10" t="s">
-        <v>2019</v>
-      </c>
-      <c r="M200" t="s">
-        <v>2020</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H201" s="10" t="s">
         <v>2021</v>
       </c>
-      <c r="B201" s="1" t="s">
+      <c r="I201" t="s">
         <v>2022</v>
       </c>
-      <c r="C201" s="1" t="s">
+      <c r="J201" t="s">
         <v>2023</v>
       </c>
-      <c r="E201" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G201" s="1" t="s">
+      <c r="K201" t="s">
         <v>2024</v>
       </c>
-      <c r="H201" s="10" t="s">
+      <c r="L201" s="10" t="s">
         <v>2025</v>
       </c>
-      <c r="I201" t="s">
+      <c r="M201" t="s">
         <v>2026</v>
-      </c>
-      <c r="J201" t="s">
-        <v>2027</v>
-      </c>
-      <c r="K201" t="s">
-        <v>2028</v>
-      </c>
-      <c r="L201" s="10" t="s">
-        <v>2029</v>
-      </c>
-      <c r="M201" t="s">
-        <v>2030</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>2030</v>
+      </c>
+      <c r="H202" s="10" t="s">
         <v>2031</v>
       </c>
-      <c r="B202" s="1" t="s">
+      <c r="I202" t="s">
         <v>2032</v>
       </c>
-      <c r="C202" s="1" t="s">
+      <c r="J202" s="11" t="s">
         <v>2033</v>
       </c>
-      <c r="E202" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G202" s="1" t="s">
+      <c r="K202" t="s">
         <v>2034</v>
       </c>
-      <c r="H202" s="10" t="s">
+      <c r="L202" s="10" t="s">
         <v>2035</v>
       </c>
-      <c r="I202" t="s">
+      <c r="M202" t="s">
         <v>2036</v>
-      </c>
-      <c r="J202" s="11" t="s">
-        <v>2037</v>
-      </c>
-      <c r="K202" t="s">
-        <v>2038</v>
-      </c>
-      <c r="L202" s="10" t="s">
-        <v>2039</v>
-      </c>
-      <c r="M202" t="s">
-        <v>2040</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H203" s="10" t="s">
         <v>2041</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="I203" t="s">
         <v>2042</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="J203" s="11" t="s">
         <v>2043</v>
       </c>
-      <c r="E203" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G203" s="1" t="s">
+      <c r="K203" t="s">
         <v>2044</v>
       </c>
-      <c r="H203" s="10" t="s">
+      <c r="L203" s="10" t="s">
         <v>2045</v>
       </c>
-      <c r="I203" t="s">
+      <c r="M203" t="s">
         <v>2046</v>
-      </c>
-      <c r="J203" s="11" t="s">
-        <v>2047</v>
-      </c>
-      <c r="K203" t="s">
-        <v>2048</v>
-      </c>
-      <c r="L203" s="10" t="s">
-        <v>2049</v>
-      </c>
-      <c r="M203" t="s">
-        <v>2050</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>2050</v>
+      </c>
+      <c r="H204" s="10" t="s">
         <v>2051</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="I204" s="23" t="s">
         <v>2052</v>
       </c>
-      <c r="C204" s="1" t="s">
+      <c r="J204" t="s">
         <v>2053</v>
       </c>
-      <c r="E204" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G204" s="1" t="s">
+      <c r="K204" t="s">
         <v>2054</v>
       </c>
-      <c r="H204" s="10" t="s">
+      <c r="L204" s="10" t="s">
         <v>2055</v>
       </c>
-      <c r="I204" s="23" t="s">
+      <c r="M204" t="s">
         <v>2056</v>
-      </c>
-      <c r="J204" t="s">
-        <v>2057</v>
-      </c>
-      <c r="K204" t="s">
-        <v>2058</v>
-      </c>
-      <c r="L204" s="10" t="s">
-        <v>2059</v>
-      </c>
-      <c r="M204" t="s">
-        <v>2060</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="H205" s="10" t="s">
         <v>2061</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="I205" t="s">
         <v>2062</v>
       </c>
-      <c r="C205" s="1" t="s">
+      <c r="J205" s="11" t="s">
         <v>2063</v>
       </c>
-      <c r="E205" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F205" s="1" t="s">
-        <v>1943</v>
-      </c>
-      <c r="G205" s="1" t="s">
+      <c r="K205" t="s">
         <v>2064</v>
       </c>
-      <c r="H205" s="10" t="s">
+      <c r="L205" s="10" t="s">
         <v>2065</v>
       </c>
-      <c r="I205" t="s">
+      <c r="M205" s="22" t="s">
         <v>2066</v>
-      </c>
-      <c r="J205" s="11" t="s">
-        <v>2067</v>
-      </c>
-      <c r="K205" t="s">
-        <v>2068</v>
-      </c>
-      <c r="L205" s="10" t="s">
-        <v>2069</v>
-      </c>
-      <c r="M205" s="22" t="s">
-        <v>2070</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F206" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="H206" s="10" t="s">
         <v>2071</v>
       </c>
-      <c r="B206" s="1" t="s">
+      <c r="I206" t="s">
         <v>2072</v>
       </c>
-      <c r="C206" s="1" t="s">
+      <c r="J206" s="10" t="s">
         <v>2073</v>
       </c>
-      <c r="E206" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F206" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G206" s="1" t="s">
+      <c r="K206" t="s">
         <v>2074</v>
       </c>
-      <c r="H206" s="10" t="s">
+      <c r="L206" s="10" t="s">
         <v>2075</v>
       </c>
-      <c r="I206" t="s">
+      <c r="M206" t="s">
         <v>2076</v>
-      </c>
-      <c r="J206" s="10" t="s">
-        <v>2077</v>
-      </c>
-      <c r="K206" t="s">
-        <v>2078</v>
-      </c>
-      <c r="L206" s="10" t="s">
-        <v>2079</v>
-      </c>
-      <c r="M206" t="s">
-        <v>2080</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>2080</v>
+      </c>
+      <c r="H207" s="10" t="s">
         <v>2081</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="I207" s="23" t="s">
         <v>2082</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="J207" s="10" t="s">
         <v>2083</v>
       </c>
-      <c r="E207" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G207" s="1" t="s">
+      <c r="K207" t="s">
         <v>2084</v>
       </c>
-      <c r="H207" s="10" t="s">
+      <c r="L207" s="10" t="s">
         <v>2085</v>
       </c>
-      <c r="I207" s="23" t="s">
+      <c r="M207" t="s">
         <v>2086</v>
-      </c>
-      <c r="J207" s="10" t="s">
-        <v>2087</v>
-      </c>
-      <c r="K207" t="s">
-        <v>2088</v>
-      </c>
-      <c r="L207" s="10" t="s">
-        <v>2089</v>
-      </c>
-      <c r="M207" t="s">
-        <v>2090</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>2090</v>
+      </c>
+      <c r="H208" s="10" t="s">
         <v>2091</v>
       </c>
-      <c r="B208" s="1" t="s">
+      <c r="I208" s="23" t="s">
         <v>2092</v>
       </c>
-      <c r="C208" s="1" t="s">
+      <c r="J208" s="18" t="s">
         <v>2093</v>
       </c>
-      <c r="E208" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G208" s="1" t="s">
+      <c r="K208" t="s">
         <v>2094</v>
       </c>
-      <c r="H208" s="10" t="s">
+      <c r="L208" s="10" t="s">
         <v>2095</v>
       </c>
-      <c r="I208" s="23" t="s">
+      <c r="M208" t="s">
         <v>2096</v>
-      </c>
-      <c r="J208" s="18" t="s">
-        <v>2097</v>
-      </c>
-      <c r="K208" t="s">
-        <v>2098</v>
-      </c>
-      <c r="L208" s="10" t="s">
-        <v>2099</v>
-      </c>
-      <c r="M208" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="H209" s="10" t="s">
         <v>2101</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="I209" s="23" t="s">
         <v>2102</v>
       </c>
-      <c r="C209" s="1" t="s">
+      <c r="J209" t="s">
         <v>2103</v>
       </c>
-      <c r="E209" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G209" s="1" t="s">
+      <c r="K209" t="s">
         <v>2104</v>
       </c>
-      <c r="H209" s="10" t="s">
+      <c r="L209" s="10" t="s">
         <v>2105</v>
       </c>
-      <c r="I209" s="23" t="s">
+      <c r="M209" t="s">
         <v>2106</v>
-      </c>
-      <c r="J209" t="s">
-        <v>2107</v>
-      </c>
-      <c r="K209" t="s">
-        <v>2108</v>
-      </c>
-      <c r="L209" s="10" t="s">
-        <v>2109</v>
-      </c>
-      <c r="M209" t="s">
-        <v>2110</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>2110</v>
+      </c>
+      <c r="H210" s="10" t="s">
         <v>2111</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="I210" t="s">
         <v>2112</v>
       </c>
-      <c r="C210" s="1" t="s">
+      <c r="J210" s="10" t="s">
         <v>2113</v>
       </c>
-      <c r="E210" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G210" s="1" t="s">
+      <c r="K210" t="s">
         <v>2114</v>
       </c>
-      <c r="H210" s="10" t="s">
+      <c r="L210" s="10" t="s">
         <v>2115</v>
       </c>
-      <c r="I210" t="s">
+      <c r="M210" t="s">
         <v>2116</v>
-      </c>
-      <c r="J210" s="10" t="s">
-        <v>2117</v>
-      </c>
-      <c r="K210" t="s">
-        <v>2118</v>
-      </c>
-      <c r="L210" s="10" t="s">
-        <v>2119</v>
-      </c>
-      <c r="M210" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>2120</v>
+      </c>
+      <c r="H211" s="10" t="s">
         <v>2121</v>
       </c>
-      <c r="B211" s="1" t="s">
+      <c r="I211" t="s">
         <v>2122</v>
       </c>
-      <c r="C211" s="1" t="s">
+      <c r="J211" s="10" t="s">
         <v>2123</v>
       </c>
-      <c r="E211" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F211" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G211" s="1" t="s">
+      <c r="K211" t="s">
         <v>2124</v>
       </c>
-      <c r="H211" s="10" t="s">
+      <c r="L211" s="10" t="s">
         <v>2125</v>
       </c>
-      <c r="I211" t="s">
+      <c r="M211" t="s">
         <v>2126</v>
-      </c>
-      <c r="J211" s="10" t="s">
-        <v>2127</v>
-      </c>
-      <c r="K211" t="s">
-        <v>2128</v>
-      </c>
-      <c r="L211" s="10" t="s">
-        <v>2129</v>
-      </c>
-      <c r="M211" t="s">
-        <v>2130</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="H212" s="10" t="s">
         <v>2131</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="I212" t="s">
         <v>2132</v>
       </c>
-      <c r="C212" s="1" t="s">
+      <c r="J212" s="11" t="s">
         <v>2133</v>
       </c>
-      <c r="E212" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G212" s="1" t="s">
+      <c r="K212" t="s">
         <v>2134</v>
       </c>
-      <c r="H212" s="10" t="s">
+      <c r="L212" s="10" t="s">
         <v>2135</v>
       </c>
-      <c r="I212" t="s">
+      <c r="M212" t="s">
         <v>2136</v>
-      </c>
-      <c r="J212" s="11" t="s">
-        <v>2137</v>
-      </c>
-      <c r="K212" t="s">
-        <v>2138</v>
-      </c>
-      <c r="L212" s="10" t="s">
-        <v>2139</v>
-      </c>
-      <c r="M212" t="s">
-        <v>2140</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>2140</v>
+      </c>
+      <c r="H213" s="10" t="s">
         <v>2141</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="I213" t="s">
         <v>2142</v>
       </c>
-      <c r="C213" s="1" t="s">
+      <c r="J213" t="s">
         <v>2143</v>
       </c>
-      <c r="E213" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F213" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G213" s="1" t="s">
+      <c r="K213" t="s">
         <v>2144</v>
       </c>
-      <c r="H213" s="10" t="s">
+      <c r="L213" s="10" t="s">
         <v>2145</v>
       </c>
-      <c r="I213" t="s">
+      <c r="M213" s="8" t="s">
         <v>2146</v>
-      </c>
-      <c r="J213" t="s">
-        <v>2147</v>
-      </c>
-      <c r="K213" t="s">
-        <v>2148</v>
-      </c>
-      <c r="L213" s="10" t="s">
-        <v>2149</v>
-      </c>
-      <c r="M213" s="8" t="s">
-        <v>2150</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="H214" s="10" t="s">
         <v>2151</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="I214" t="s">
         <v>2152</v>
       </c>
-      <c r="C214" s="1" t="s">
+      <c r="J214" t="s">
         <v>2153</v>
       </c>
-      <c r="E214" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F214" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G214" s="1" t="s">
+      <c r="K214" t="s">
         <v>2154</v>
       </c>
-      <c r="H214" s="10" t="s">
+      <c r="L214" s="10" t="s">
         <v>2155</v>
       </c>
-      <c r="I214" t="s">
+      <c r="M214" t="s">
         <v>2156</v>
-      </c>
-      <c r="J214" t="s">
-        <v>2157</v>
-      </c>
-      <c r="K214" t="s">
-        <v>2158</v>
-      </c>
-      <c r="L214" s="10" t="s">
-        <v>2159</v>
-      </c>
-      <c r="M214" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>2159</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F215" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>2160</v>
+      </c>
+      <c r="H215" s="10" t="s">
         <v>2161</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="I215" t="s">
         <v>2162</v>
       </c>
-      <c r="C215" s="1" t="s">
+      <c r="J215" t="s">
         <v>2163</v>
       </c>
-      <c r="E215" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F215" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G215" s="1" t="s">
+      <c r="K215" t="s">
         <v>2164</v>
       </c>
-      <c r="H215" s="10" t="s">
+      <c r="L215" s="10" t="s">
         <v>2165</v>
       </c>
-      <c r="I215" t="s">
+      <c r="M215" s="8" t="s">
         <v>2166</v>
-      </c>
-      <c r="J215" t="s">
-        <v>2167</v>
-      </c>
-      <c r="K215" t="s">
-        <v>2168</v>
-      </c>
-      <c r="L215" s="10" t="s">
-        <v>2169</v>
-      </c>
-      <c r="M215" s="8" t="s">
-        <v>2170</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>2170</v>
+      </c>
+      <c r="H216" s="10" t="s">
         <v>2171</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="I216" t="s">
         <v>2172</v>
       </c>
-      <c r="C216" s="1" t="s">
+      <c r="J216" t="s">
         <v>2173</v>
       </c>
-      <c r="E216" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F216" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G216" s="1" t="s">
+      <c r="K216" t="s">
         <v>2174</v>
       </c>
-      <c r="H216" s="10" t="s">
+      <c r="L216" s="10" t="s">
         <v>2175</v>
       </c>
-      <c r="I216" t="s">
+      <c r="M216" t="s">
         <v>2176</v>
-      </c>
-      <c r="J216" t="s">
-        <v>2177</v>
-      </c>
-      <c r="K216" t="s">
-        <v>2178</v>
-      </c>
-      <c r="L216" s="10" t="s">
-        <v>2179</v>
-      </c>
-      <c r="M216" t="s">
-        <v>2180</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>2180</v>
+      </c>
+      <c r="H217" s="10" t="s">
         <v>2181</v>
       </c>
-      <c r="B217" s="1" t="s">
+      <c r="I217" t="s">
         <v>2182</v>
       </c>
-      <c r="C217" s="1" t="s">
+      <c r="J217" s="18" t="s">
         <v>2183</v>
       </c>
-      <c r="E217" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F217" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G217" s="1" t="s">
+      <c r="K217" t="s">
         <v>2184</v>
       </c>
-      <c r="H217" s="10" t="s">
+      <c r="L217" s="10" t="s">
         <v>2185</v>
       </c>
-      <c r="I217" t="s">
+      <c r="M217" t="s">
         <v>2186</v>
-      </c>
-      <c r="J217" s="18" t="s">
-        <v>2187</v>
-      </c>
-      <c r="K217" t="s">
-        <v>2188</v>
-      </c>
-      <c r="L217" s="10" t="s">
-        <v>2189</v>
-      </c>
-      <c r="M217" t="s">
-        <v>2190</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F218" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>2190</v>
+      </c>
+      <c r="H218" s="10" t="s">
         <v>2191</v>
       </c>
-      <c r="B218" s="1" t="s">
+      <c r="I218" t="s">
         <v>2192</v>
       </c>
-      <c r="C218" s="1" t="s">
+      <c r="J218" t="s">
         <v>2193</v>
       </c>
-      <c r="E218" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F218" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G218" s="1" t="s">
+      <c r="K218" t="s">
         <v>2194</v>
       </c>
-      <c r="H218" s="10" t="s">
+      <c r="L218" s="10" t="s">
         <v>2195</v>
       </c>
-      <c r="I218" t="s">
+      <c r="M218" s="7" t="s">
         <v>2196</v>
-      </c>
-      <c r="J218" t="s">
-        <v>2197</v>
-      </c>
-      <c r="K218" t="s">
-        <v>2198</v>
-      </c>
-      <c r="L218" s="10" t="s">
-        <v>2199</v>
-      </c>
-      <c r="M218" s="7" t="s">
-        <v>2200</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>2200</v>
+      </c>
+      <c r="H219" s="10" t="s">
         <v>2201</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="I219" t="s">
         <v>2202</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="J219" t="s">
         <v>2203</v>
       </c>
-      <c r="E219" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F219" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G219" s="1" t="s">
+      <c r="K219" t="s">
         <v>2204</v>
       </c>
-      <c r="H219" s="10" t="s">
+      <c r="L219" s="10" t="s">
         <v>2205</v>
       </c>
-      <c r="I219" t="s">
+      <c r="M219" s="8" t="s">
         <v>2206</v>
-      </c>
-      <c r="J219" t="s">
-        <v>2207</v>
-      </c>
-      <c r="K219" t="s">
-        <v>2208</v>
-      </c>
-      <c r="L219" s="10" t="s">
-        <v>2209</v>
-      </c>
-      <c r="M219" s="8" t="s">
-        <v>2210</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>2210</v>
+      </c>
+      <c r="H220" s="10" t="s">
         <v>2211</v>
       </c>
-      <c r="B220" s="1" t="s">
+      <c r="I220" t="s">
         <v>2212</v>
       </c>
-      <c r="C220" s="1" t="s">
+      <c r="J220" t="s">
         <v>2213</v>
       </c>
-      <c r="E220" s="1" t="s">
-        <v>1829</v>
-      </c>
-      <c r="F220" s="1" t="s">
-        <v>1830</v>
-      </c>
-      <c r="G220" s="1" t="s">
+      <c r="K220" t="s">
         <v>2214</v>
       </c>
-      <c r="H220" s="10" t="s">
+      <c r="L220" s="10" t="s">
         <v>2215</v>
       </c>
-      <c r="I220" t="s">
+      <c r="M220" s="8" t="s">
         <v>2216</v>
-      </c>
-      <c r="J220" t="s">
-        <v>2217</v>
-      </c>
-      <c r="K220" t="s">
-        <v>2218</v>
-      </c>
-      <c r="L220" s="10" t="s">
-        <v>2219</v>
-      </c>
-      <c r="M220" s="8" t="s">
-        <v>2220</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>2221</v>
+        <v>2217</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>2222</v>
+        <v>2218</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>2223</v>
+        <v>2219</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F221" s="1" t="s">
+        <v>2220</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>2221</v>
+      </c>
+      <c r="H221" s="10" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I221" t="s">
+        <v>2223</v>
+      </c>
+      <c r="J221" t="s">
         <v>2224</v>
       </c>
-      <c r="G221" s="1" t="s">
+      <c r="K221" t="s">
         <v>2225</v>
       </c>
-      <c r="H221" s="10" t="s">
+      <c r="L221" s="10" t="s">
         <v>2226</v>
       </c>
-      <c r="I221" t="s">
+      <c r="M221" t="s">
         <v>2227</v>
-      </c>
-      <c r="J221" t="s">
-        <v>2228</v>
-      </c>
-      <c r="K221" t="s">
-        <v>2229</v>
-      </c>
-      <c r="L221" s="10" t="s">
-        <v>2230</v>
-      </c>
-      <c r="M221" t="s">
-        <v>2231</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>2232</v>
+        <v>2228</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>2233</v>
+        <v>2229</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>2234</v>
+        <v>2230</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F222" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="H222" s="10" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I222" t="s">
+        <v>2234</v>
+      </c>
+      <c r="J222" t="s">
         <v>2235</v>
       </c>
-      <c r="G222" s="1" t="s">
+      <c r="K222" t="s">
         <v>2236</v>
       </c>
-      <c r="H222" s="10" t="s">
+      <c r="L222" s="10" t="s">
         <v>2237</v>
       </c>
-      <c r="I222" t="s">
+      <c r="M222" t="s">
         <v>2238</v>
-      </c>
-      <c r="J222" t="s">
-        <v>2239</v>
-      </c>
-      <c r="K222" t="s">
-        <v>2240</v>
-      </c>
-      <c r="L222" s="10" t="s">
-        <v>2241</v>
-      </c>
-      <c r="M222" t="s">
-        <v>2242</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>2243</v>
+        <v>2239</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>2244</v>
+        <v>2240</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>2245</v>
+        <v>2241</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G223" s="1" t="s">
+        <v>2242</v>
+      </c>
+      <c r="H223" s="10" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I223" t="s">
+        <v>2244</v>
+      </c>
+      <c r="J223" t="s">
+        <v>2245</v>
+      </c>
+      <c r="K223" t="s">
         <v>2246</v>
       </c>
-      <c r="H223" s="10" t="s">
+      <c r="L223" s="10" t="s">
         <v>2247</v>
       </c>
-      <c r="I223" t="s">
+      <c r="M223" t="s">
         <v>2248</v>
-      </c>
-      <c r="J223" t="s">
-        <v>2249</v>
-      </c>
-      <c r="K223" t="s">
-        <v>2250</v>
-      </c>
-      <c r="L223" s="10" t="s">
-        <v>2251</v>
-      </c>
-      <c r="M223" t="s">
-        <v>2252</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>2253</v>
+        <v>2249</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>2254</v>
+        <v>2250</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>2255</v>
+        <v>2251</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G224" s="1" t="s">
+        <v>2252</v>
+      </c>
+      <c r="H224" s="10" t="s">
+        <v>2253</v>
+      </c>
+      <c r="I224" t="s">
+        <v>2254</v>
+      </c>
+      <c r="J224" t="s">
+        <v>2255</v>
+      </c>
+      <c r="K224" t="s">
         <v>2256</v>
       </c>
-      <c r="H224" s="10" t="s">
+      <c r="L224" s="10" t="s">
         <v>2257</v>
       </c>
-      <c r="I224" t="s">
+      <c r="M224" s="22" t="s">
         <v>2258</v>
-      </c>
-      <c r="J224" t="s">
-        <v>2259</v>
-      </c>
-      <c r="K224" t="s">
-        <v>2260</v>
-      </c>
-      <c r="L224" s="10" t="s">
-        <v>2261</v>
-      </c>
-      <c r="M224" s="22" t="s">
-        <v>2262</v>
       </c>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>2263</v>
+        <v>2259</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>2264</v>
+        <v>2260</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>2265</v>
+        <v>2261</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G225" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="H225" s="10" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I225" t="s">
+        <v>2264</v>
+      </c>
+      <c r="J225" t="s">
+        <v>2265</v>
+      </c>
+      <c r="K225" t="s">
         <v>2266</v>
       </c>
-      <c r="H225" s="10" t="s">
+      <c r="L225" s="10" t="s">
         <v>2267</v>
       </c>
-      <c r="I225" t="s">
+      <c r="M225" t="s">
         <v>2268</v>
-      </c>
-      <c r="J225" t="s">
-        <v>2269</v>
-      </c>
-      <c r="K225" t="s">
-        <v>2270</v>
-      </c>
-      <c r="L225" s="10" t="s">
-        <v>2271</v>
-      </c>
-      <c r="M225" t="s">
-        <v>2272</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>2273</v>
+        <v>2269</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>2274</v>
+        <v>2270</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G226" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="H226" s="10" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I226" t="s">
+        <v>2274</v>
+      </c>
+      <c r="J226" t="s">
+        <v>2275</v>
+      </c>
+      <c r="K226" t="s">
         <v>2276</v>
       </c>
-      <c r="H226" s="10" t="s">
+      <c r="L226" s="10" t="s">
         <v>2277</v>
       </c>
-      <c r="I226" t="s">
+      <c r="M226" t="s">
         <v>2278</v>
-      </c>
-      <c r="J226" t="s">
-        <v>2279</v>
-      </c>
-      <c r="K226" t="s">
-        <v>2280</v>
-      </c>
-      <c r="L226" s="10" t="s">
-        <v>2281</v>
-      </c>
-      <c r="M226" t="s">
-        <v>2282</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>2283</v>
+        <v>2279</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>2284</v>
+        <v>2280</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>2285</v>
+        <v>2281</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F227" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="H227" s="10" t="s">
+        <v>2284</v>
+      </c>
+      <c r="I227" t="s">
+        <v>2285</v>
+      </c>
+      <c r="J227" s="10" t="s">
         <v>2286</v>
       </c>
-      <c r="G227" s="1" t="s">
+      <c r="K227" t="s">
         <v>2287</v>
       </c>
-      <c r="H227" s="10" t="s">
+      <c r="L227" s="10" t="s">
         <v>2288</v>
       </c>
-      <c r="I227" t="s">
+      <c r="M227" s="8" t="s">
         <v>2289</v>
-      </c>
-      <c r="J227" s="10" t="s">
-        <v>2290</v>
-      </c>
-      <c r="K227" t="s">
-        <v>2291</v>
-      </c>
-      <c r="L227" s="10" t="s">
-        <v>2292</v>
-      </c>
-      <c r="M227" s="8" t="s">
-        <v>2293</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>2294</v>
+        <v>2290</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>2295</v>
+        <v>2291</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>2296</v>
+        <v>2292</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>54</v>
@@ -18147,302 +18147,302 @@
         <v>55</v>
       </c>
       <c r="G228" s="1" t="s">
+        <v>2293</v>
+      </c>
+      <c r="H228" s="10" t="s">
+        <v>2294</v>
+      </c>
+      <c r="I228" s="2" t="s">
+        <v>2295</v>
+      </c>
+      <c r="J228" s="18" t="s">
+        <v>2296</v>
+      </c>
+      <c r="K228" t="s">
         <v>2297</v>
       </c>
-      <c r="H228" s="10" t="s">
+      <c r="L228" s="10" t="s">
         <v>2298</v>
       </c>
-      <c r="I228" s="2" t="s">
+      <c r="M228" s="8" t="s">
         <v>2299</v>
-      </c>
-      <c r="J228" s="18" t="s">
-        <v>2300</v>
-      </c>
-      <c r="K228" t="s">
-        <v>2301</v>
-      </c>
-      <c r="L228" s="10" t="s">
-        <v>2302</v>
-      </c>
-      <c r="M228" s="8" t="s">
-        <v>2303</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>2304</v>
+        <v>2300</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>2305</v>
+        <v>2301</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>2306</v>
+        <v>2302</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="G229" s="1" t="s">
+        <v>2303</v>
+      </c>
+      <c r="H229" s="10" t="s">
+        <v>2304</v>
+      </c>
+      <c r="I229" t="s">
+        <v>2305</v>
+      </c>
+      <c r="J229" s="10" t="s">
+        <v>2306</v>
+      </c>
+      <c r="K229" t="s">
         <v>2307</v>
       </c>
-      <c r="H229" s="10" t="s">
+      <c r="L229" s="10" t="s">
         <v>2308</v>
       </c>
-      <c r="I229" t="s">
+      <c r="M229" t="s">
         <v>2309</v>
-      </c>
-      <c r="J229" s="10" t="s">
-        <v>2310</v>
-      </c>
-      <c r="K229" t="s">
-        <v>2311</v>
-      </c>
-      <c r="L229" s="10" t="s">
-        <v>2312</v>
-      </c>
-      <c r="M229" t="s">
-        <v>2313</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>2314</v>
+        <v>2310</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>2315</v>
+        <v>2311</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>2316</v>
+        <v>2312</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="G230" s="1" t="s">
+        <v>2313</v>
+      </c>
+      <c r="H230" s="10" t="s">
+        <v>2314</v>
+      </c>
+      <c r="I230" s="2" t="s">
+        <v>2315</v>
+      </c>
+      <c r="J230" t="s">
+        <v>2316</v>
+      </c>
+      <c r="K230" t="s">
         <v>2317</v>
       </c>
-      <c r="H230" s="10" t="s">
+      <c r="L230" s="10" t="s">
         <v>2318</v>
       </c>
-      <c r="I230" s="2" t="s">
+      <c r="M230" t="s">
         <v>2319</v>
-      </c>
-      <c r="J230" t="s">
-        <v>2320</v>
-      </c>
-      <c r="K230" t="s">
-        <v>2321</v>
-      </c>
-      <c r="L230" s="10" t="s">
-        <v>2322</v>
-      </c>
-      <c r="M230" t="s">
-        <v>2323</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>2324</v>
+        <v>2320</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>2325</v>
+        <v>2321</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>2326</v>
+        <v>2322</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="G231" s="1" t="s">
+        <v>2323</v>
+      </c>
+      <c r="H231" s="10" t="s">
+        <v>2324</v>
+      </c>
+      <c r="I231" t="s">
+        <v>2325</v>
+      </c>
+      <c r="J231" t="s">
+        <v>2326</v>
+      </c>
+      <c r="K231" t="s">
         <v>2327</v>
       </c>
-      <c r="H231" s="10" t="s">
+      <c r="L231" s="10" t="s">
         <v>2328</v>
       </c>
-      <c r="I231" t="s">
+      <c r="M231" t="s">
         <v>2329</v>
-      </c>
-      <c r="J231" t="s">
-        <v>2330</v>
-      </c>
-      <c r="K231" t="s">
-        <v>2331</v>
-      </c>
-      <c r="L231" s="10" t="s">
-        <v>2332</v>
-      </c>
-      <c r="M231" t="s">
-        <v>2333</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>2334</v>
+        <v>2330</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>2335</v>
+        <v>2331</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>2336</v>
+        <v>2332</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G232" s="1" t="s">
+        <v>2333</v>
+      </c>
+      <c r="H232" s="10" t="s">
+        <v>2334</v>
+      </c>
+      <c r="I232" t="s">
+        <v>2335</v>
+      </c>
+      <c r="J232" s="10" t="s">
+        <v>2336</v>
+      </c>
+      <c r="K232" t="s">
         <v>2337</v>
       </c>
-      <c r="H232" s="10" t="s">
+      <c r="L232" s="10" t="s">
         <v>2338</v>
       </c>
-      <c r="I232" t="s">
+      <c r="M232" t="s">
         <v>2339</v>
-      </c>
-      <c r="J232" s="10" t="s">
-        <v>2340</v>
-      </c>
-      <c r="K232" t="s">
-        <v>2341</v>
-      </c>
-      <c r="L232" s="10" t="s">
-        <v>2342</v>
-      </c>
-      <c r="M232" t="s">
-        <v>2343</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>2344</v>
+        <v>2340</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>2345</v>
+        <v>2341</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>2346</v>
+        <v>2342</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
       <c r="G233" s="1" t="s">
+        <v>2343</v>
+      </c>
+      <c r="H233" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="I233" t="s">
+        <v>2345</v>
+      </c>
+      <c r="J233" t="s">
+        <v>2346</v>
+      </c>
+      <c r="K233" t="s">
         <v>2347</v>
       </c>
-      <c r="H233" s="10" t="s">
+      <c r="L233" s="10" t="s">
         <v>2348</v>
       </c>
-      <c r="I233" t="s">
+      <c r="M233" t="s">
         <v>2349</v>
-      </c>
-      <c r="J233" t="s">
-        <v>2350</v>
-      </c>
-      <c r="K233" t="s">
-        <v>2351</v>
-      </c>
-      <c r="L233" s="10" t="s">
-        <v>2352</v>
-      </c>
-      <c r="M233" t="s">
-        <v>2353</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>2354</v>
+        <v>2350</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>2355</v>
+        <v>2351</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>2356</v>
+        <v>2352</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="G234" s="1" t="s">
+        <v>2353</v>
+      </c>
+      <c r="H234" s="10" t="s">
+        <v>2354</v>
+      </c>
+      <c r="I234" t="s">
+        <v>2355</v>
+      </c>
+      <c r="J234" t="s">
+        <v>2356</v>
+      </c>
+      <c r="K234" t="s">
         <v>2357</v>
       </c>
-      <c r="H234" s="10" t="s">
+      <c r="L234" s="10" t="s">
         <v>2358</v>
       </c>
-      <c r="I234" t="s">
+      <c r="M234" t="s">
         <v>2359</v>
-      </c>
-      <c r="J234" t="s">
-        <v>2360</v>
-      </c>
-      <c r="K234" t="s">
-        <v>2361</v>
-      </c>
-      <c r="L234" s="10" t="s">
-        <v>2362</v>
-      </c>
-      <c r="M234" t="s">
-        <v>2363</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>2364</v>
+        <v>2360</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>2366</v>
+        <v>2362</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="G235" s="1" t="s">
+        <v>2363</v>
+      </c>
+      <c r="H235" s="10" t="s">
+        <v>2364</v>
+      </c>
+      <c r="I235" s="24" t="s">
+        <v>2365</v>
+      </c>
+      <c r="J235" t="s">
+        <v>2366</v>
+      </c>
+      <c r="K235" t="s">
         <v>2367</v>
       </c>
-      <c r="H235" s="10" t="s">
+      <c r="L235" s="12" t="s">
         <v>2368</v>
       </c>
-      <c r="I235" s="24" t="s">
+      <c r="M235" t="s">
         <v>2369</v>
-      </c>
-      <c r="J235" t="s">
-        <v>2370</v>
-      </c>
-      <c r="K235" t="s">
-        <v>2371</v>
-      </c>
-      <c r="L235" s="12" t="s">
-        <v>2372</v>
-      </c>
-      <c r="M235" t="s">
-        <v>2373</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>2375</v>
+        <v>2371</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>2376</v>
+        <v>2372</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>564</v>
@@ -18451,36 +18451,36 @@
         <v>564</v>
       </c>
       <c r="G236" s="1" t="s">
+        <v>2373</v>
+      </c>
+      <c r="H236" s="10" t="s">
+        <v>2374</v>
+      </c>
+      <c r="I236" t="s">
+        <v>2375</v>
+      </c>
+      <c r="J236" t="s">
+        <v>2376</v>
+      </c>
+      <c r="K236" t="s">
         <v>2377</v>
       </c>
-      <c r="H236" s="10" t="s">
+      <c r="L236" s="10" t="s">
         <v>2378</v>
       </c>
-      <c r="I236" t="s">
+      <c r="M236" t="s">
         <v>2379</v>
-      </c>
-      <c r="J236" t="s">
-        <v>2380</v>
-      </c>
-      <c r="K236" t="s">
-        <v>2381</v>
-      </c>
-      <c r="L236" s="10" t="s">
-        <v>2382</v>
-      </c>
-      <c r="M236" t="s">
-        <v>2383</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>2385</v>
+        <v>2381</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>2386</v>
+        <v>2382</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>15</v>
@@ -18489,36 +18489,36 @@
         <v>26</v>
       </c>
       <c r="G237" s="1" t="s">
+        <v>2383</v>
+      </c>
+      <c r="H237" s="10" t="s">
+        <v>2384</v>
+      </c>
+      <c r="I237" t="s">
+        <v>2385</v>
+      </c>
+      <c r="J237" t="s">
+        <v>2386</v>
+      </c>
+      <c r="K237" t="s">
         <v>2387</v>
       </c>
-      <c r="H237" s="10" t="s">
+      <c r="L237" s="10" t="s">
         <v>2388</v>
       </c>
-      <c r="I237" t="s">
+      <c r="M237" t="s">
         <v>2389</v>
-      </c>
-      <c r="J237" t="s">
-        <v>2390</v>
-      </c>
-      <c r="K237" t="s">
-        <v>2391</v>
-      </c>
-      <c r="L237" s="10" t="s">
-        <v>2392</v>
-      </c>
-      <c r="M237" t="s">
-        <v>2393</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>2394</v>
+        <v>2390</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>2395</v>
+        <v>2391</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>2396</v>
+        <v>2392</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>15</v>
@@ -18527,439 +18527,439 @@
         <v>74</v>
       </c>
       <c r="G238" s="1" t="s">
+        <v>2393</v>
+      </c>
+      <c r="H238" s="10" t="s">
+        <v>2394</v>
+      </c>
+      <c r="I238" s="2" t="s">
+        <v>2395</v>
+      </c>
+      <c r="J238" s="18" t="s">
+        <v>2396</v>
+      </c>
+      <c r="K238" t="s">
         <v>2397</v>
       </c>
-      <c r="H238" s="10" t="s">
+      <c r="L238" s="10" t="s">
         <v>2398</v>
       </c>
-      <c r="I238" s="2" t="s">
+      <c r="M238" t="s">
         <v>2399</v>
-      </c>
-      <c r="J238" s="18" t="s">
-        <v>2400</v>
-      </c>
-      <c r="K238" t="s">
-        <v>2401</v>
-      </c>
-      <c r="L238" s="10" t="s">
-        <v>2402</v>
-      </c>
-      <c r="M238" t="s">
-        <v>2403</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>2404</v>
+        <v>2400</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>2405</v>
+        <v>2401</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>2406</v>
+        <v>2402</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
       <c r="G239" s="1" t="s">
+        <v>2403</v>
+      </c>
+      <c r="H239" s="10" t="s">
+        <v>2404</v>
+      </c>
+      <c r="I239" s="2" t="s">
+        <v>2405</v>
+      </c>
+      <c r="J239" t="s">
+        <v>2406</v>
+      </c>
+      <c r="K239" t="s">
         <v>2407</v>
       </c>
-      <c r="H239" s="10" t="s">
+      <c r="L239" s="10" t="s">
         <v>2408</v>
       </c>
-      <c r="I239" s="2" t="s">
+      <c r="M239" s="8" t="s">
         <v>2409</v>
-      </c>
-      <c r="J239" t="s">
-        <v>2410</v>
-      </c>
-      <c r="K239" t="s">
-        <v>2411</v>
-      </c>
-      <c r="L239" s="10" t="s">
-        <v>2412</v>
-      </c>
-      <c r="M239" s="8" t="s">
-        <v>2413</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>2414</v>
+        <v>2410</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>2415</v>
+        <v>2411</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>2416</v>
+        <v>2412</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
       <c r="G240" s="1" t="s">
+        <v>2413</v>
+      </c>
+      <c r="H240" s="10" t="s">
+        <v>2414</v>
+      </c>
+      <c r="I240" t="s">
+        <v>2415</v>
+      </c>
+      <c r="J240" t="s">
+        <v>2416</v>
+      </c>
+      <c r="K240" t="s">
         <v>2417</v>
       </c>
-      <c r="H240" s="10" t="s">
+      <c r="L240" s="10" t="s">
         <v>2418</v>
       </c>
-      <c r="I240" t="s">
+      <c r="M240" s="8" t="s">
         <v>2419</v>
-      </c>
-      <c r="J240" t="s">
-        <v>2420</v>
-      </c>
-      <c r="K240" t="s">
-        <v>2421</v>
-      </c>
-      <c r="L240" s="10" t="s">
-        <v>2422</v>
-      </c>
-      <c r="M240" s="8" t="s">
-        <v>2423</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>2424</v>
+        <v>2420</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>2425</v>
+        <v>2421</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>2426</v>
+        <v>2422</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G241" s="1" t="s">
+        <v>2423</v>
+      </c>
+      <c r="H241" s="10" t="s">
+        <v>2424</v>
+      </c>
+      <c r="I241" t="s">
+        <v>2425</v>
+      </c>
+      <c r="J241" t="s">
+        <v>2426</v>
+      </c>
+      <c r="K241" t="s">
         <v>2427</v>
       </c>
-      <c r="H241" s="10" t="s">
+      <c r="L241" s="10" t="s">
         <v>2428</v>
       </c>
-      <c r="I241" t="s">
+      <c r="M241" t="s">
         <v>2429</v>
-      </c>
-      <c r="J241" t="s">
-        <v>2430</v>
-      </c>
-      <c r="K241" t="s">
-        <v>2431</v>
-      </c>
-      <c r="L241" s="10" t="s">
-        <v>2432</v>
-      </c>
-      <c r="M241" t="s">
-        <v>2433</v>
       </c>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>2434</v>
+        <v>2430</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>2435</v>
+        <v>2431</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>2436</v>
+        <v>2432</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G242" s="1" t="s">
+        <v>2433</v>
+      </c>
+      <c r="H242" s="10" t="s">
+        <v>2434</v>
+      </c>
+      <c r="I242" t="s">
+        <v>2435</v>
+      </c>
+      <c r="J242" t="s">
+        <v>2436</v>
+      </c>
+      <c r="K242" t="s">
         <v>2437</v>
       </c>
-      <c r="H242" s="10" t="s">
+      <c r="L242" s="10" t="s">
         <v>2438</v>
       </c>
-      <c r="I242" t="s">
+      <c r="M242" s="8" t="s">
         <v>2439</v>
-      </c>
-      <c r="J242" t="s">
-        <v>2440</v>
-      </c>
-      <c r="K242" t="s">
-        <v>2441</v>
-      </c>
-      <c r="L242" s="10" t="s">
-        <v>2442</v>
-      </c>
-      <c r="M242" s="8" t="s">
-        <v>2443</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>2444</v>
+        <v>2440</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>2445</v>
+        <v>2441</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>2446</v>
+        <v>2442</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G243" s="1" t="s">
+        <v>2443</v>
+      </c>
+      <c r="H243" s="10" t="s">
+        <v>2444</v>
+      </c>
+      <c r="I243" s="10" t="s">
+        <v>2445</v>
+      </c>
+      <c r="J243" t="s">
+        <v>2446</v>
+      </c>
+      <c r="K243" t="s">
         <v>2447</v>
       </c>
-      <c r="H243" s="10" t="s">
+      <c r="L243" s="10" t="s">
         <v>2448</v>
       </c>
-      <c r="I243" s="10" t="s">
+      <c r="M243" t="s">
         <v>2449</v>
-      </c>
-      <c r="J243" t="s">
-        <v>2450</v>
-      </c>
-      <c r="K243" t="s">
-        <v>2451</v>
-      </c>
-      <c r="L243" s="10" t="s">
-        <v>2452</v>
-      </c>
-      <c r="M243" t="s">
-        <v>2453</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>2454</v>
+        <v>2450</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>2455</v>
+        <v>2451</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>2456</v>
+        <v>2452</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G244" s="1" t="s">
+        <v>2453</v>
+      </c>
+      <c r="H244" s="10" t="s">
+        <v>2454</v>
+      </c>
+      <c r="I244" t="s">
+        <v>2455</v>
+      </c>
+      <c r="J244" t="s">
+        <v>2456</v>
+      </c>
+      <c r="K244" t="s">
         <v>2457</v>
       </c>
-      <c r="H244" s="10" t="s">
+      <c r="L244" s="10" t="s">
         <v>2458</v>
       </c>
-      <c r="I244" t="s">
+      <c r="M244" t="s">
         <v>2459</v>
-      </c>
-      <c r="J244" t="s">
-        <v>2460</v>
-      </c>
-      <c r="K244" t="s">
-        <v>2461</v>
-      </c>
-      <c r="L244" s="10" t="s">
-        <v>2462</v>
-      </c>
-      <c r="M244" t="s">
-        <v>2463</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>2464</v>
+        <v>2460</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>2465</v>
+        <v>2461</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>2466</v>
+        <v>2462</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G245" s="1" t="s">
+        <v>2463</v>
+      </c>
+      <c r="H245" s="10" t="s">
+        <v>2464</v>
+      </c>
+      <c r="I245" t="s">
+        <v>2465</v>
+      </c>
+      <c r="J245" t="s">
+        <v>2466</v>
+      </c>
+      <c r="K245" t="s">
         <v>2467</v>
       </c>
-      <c r="H245" s="10" t="s">
+      <c r="L245" s="10" t="s">
         <v>2468</v>
       </c>
-      <c r="I245" t="s">
+      <c r="M245" t="s">
         <v>2469</v>
-      </c>
-      <c r="J245" t="s">
-        <v>2470</v>
-      </c>
-      <c r="K245" t="s">
-        <v>2471</v>
-      </c>
-      <c r="L245" s="10" t="s">
-        <v>2472</v>
-      </c>
-      <c r="M245" t="s">
-        <v>2473</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>2474</v>
+        <v>2470</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>2475</v>
+        <v>2471</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G246" s="1" t="s">
+        <v>2472</v>
+      </c>
+      <c r="H246" s="10" t="s">
+        <v>2473</v>
+      </c>
+      <c r="I246" s="24" t="s">
+        <v>2474</v>
+      </c>
+      <c r="J246" t="s">
+        <v>2475</v>
+      </c>
+      <c r="K246" t="s">
         <v>2476</v>
       </c>
-      <c r="H246" s="10" t="s">
+      <c r="L246" s="10" t="s">
         <v>2477</v>
       </c>
-      <c r="I246" s="24" t="s">
+      <c r="M246" t="s">
         <v>2478</v>
-      </c>
-      <c r="J246" t="s">
-        <v>2479</v>
-      </c>
-      <c r="K246" t="s">
-        <v>2480</v>
-      </c>
-      <c r="L246" s="10" t="s">
-        <v>2481</v>
-      </c>
-      <c r="M246" t="s">
-        <v>2482</v>
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>2483</v>
+        <v>2479</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>2484</v>
+        <v>2480</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G247" s="1" t="s">
+        <v>2481</v>
+      </c>
+      <c r="H247" s="10" t="s">
+        <v>2482</v>
+      </c>
+      <c r="I247" t="s">
+        <v>2483</v>
+      </c>
+      <c r="J247" t="s">
+        <v>2484</v>
+      </c>
+      <c r="K247" t="s">
         <v>2485</v>
       </c>
-      <c r="H247" s="10" t="s">
+      <c r="L247" s="10" t="s">
         <v>2486</v>
       </c>
-      <c r="I247" t="s">
+      <c r="M247" s="22" t="s">
         <v>2487</v>
-      </c>
-      <c r="J247" t="s">
-        <v>2488</v>
-      </c>
-      <c r="K247" t="s">
-        <v>2489</v>
-      </c>
-      <c r="L247" s="10" t="s">
-        <v>2490</v>
-      </c>
-      <c r="M247" s="22" t="s">
-        <v>2491</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>2492</v>
+        <v>2488</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>2493</v>
+        <v>2489</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G248" s="1" t="s">
+        <v>2490</v>
+      </c>
+      <c r="H248" s="10" t="s">
+        <v>2491</v>
+      </c>
+      <c r="I248" s="2" t="s">
+        <v>2492</v>
+      </c>
+      <c r="J248" t="s">
+        <v>2493</v>
+      </c>
+      <c r="K248" t="s">
         <v>2494</v>
       </c>
-      <c r="H248" s="10" t="s">
+      <c r="L248" s="10" t="s">
         <v>2495</v>
       </c>
-      <c r="I248" s="2" t="s">
+      <c r="M248" t="s">
         <v>2496</v>
-      </c>
-      <c r="J248" t="s">
-        <v>2497</v>
-      </c>
-      <c r="K248" t="s">
-        <v>2498</v>
-      </c>
-      <c r="L248" s="10" t="s">
-        <v>2499</v>
-      </c>
-      <c r="M248" t="s">
-        <v>2500</v>
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>2501</v>
+        <v>2497</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>2502</v>
+        <v>2498</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G249" s="1" t="s">
+        <v>2499</v>
+      </c>
+      <c r="H249" s="10" t="s">
+        <v>2500</v>
+      </c>
+      <c r="I249" s="2" t="s">
+        <v>2501</v>
+      </c>
+      <c r="J249" t="s">
+        <v>2502</v>
+      </c>
+      <c r="K249" t="s">
         <v>2503</v>
       </c>
-      <c r="H249" s="10" t="s">
+      <c r="L249" s="10" t="s">
         <v>2504</v>
       </c>
-      <c r="I249" s="2" t="s">
+      <c r="M249" t="s">
         <v>2505</v>
-      </c>
-      <c r="J249" t="s">
-        <v>2506</v>
-      </c>
-      <c r="K249" t="s">
-        <v>2507</v>
-      </c>
-      <c r="L249" s="10" t="s">
-        <v>2508</v>
-      </c>
-      <c r="M249" t="s">
-        <v>2509</v>
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>2510</v>
+        <v>2506</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>2511</v>
+        <v>2507</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>54</v>
@@ -18968,33 +18968,33 @@
         <v>55</v>
       </c>
       <c r="G250" s="1" t="s">
+        <v>2508</v>
+      </c>
+      <c r="H250" s="10" t="s">
+        <v>2509</v>
+      </c>
+      <c r="I250" s="10" t="s">
+        <v>2510</v>
+      </c>
+      <c r="J250" t="s">
+        <v>2511</v>
+      </c>
+      <c r="K250" t="s">
         <v>2512</v>
       </c>
-      <c r="H250" s="10" t="s">
+      <c r="L250" s="10" t="s">
         <v>2513</v>
       </c>
-      <c r="I250" s="10" t="s">
+      <c r="M250" t="s">
         <v>2514</v>
-      </c>
-      <c r="J250" t="s">
-        <v>2515</v>
-      </c>
-      <c r="K250" t="s">
-        <v>2516</v>
-      </c>
-      <c r="L250" s="10" t="s">
-        <v>2517</v>
-      </c>
-      <c r="M250" t="s">
-        <v>2518</v>
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>2519</v>
+        <v>2515</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>2520</v>
+        <v>2516</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>54</v>
@@ -19003,33 +19003,33 @@
         <v>55</v>
       </c>
       <c r="G251" s="1" t="s">
+        <v>2517</v>
+      </c>
+      <c r="H251" s="10" t="s">
+        <v>2518</v>
+      </c>
+      <c r="I251" s="2" t="s">
+        <v>2519</v>
+      </c>
+      <c r="J251" t="s">
+        <v>2520</v>
+      </c>
+      <c r="K251" t="s">
         <v>2521</v>
       </c>
-      <c r="H251" s="10" t="s">
+      <c r="L251" s="10" t="s">
         <v>2522</v>
       </c>
-      <c r="I251" s="2" t="s">
+      <c r="M251" s="8" t="s">
         <v>2523</v>
-      </c>
-      <c r="J251" t="s">
-        <v>2524</v>
-      </c>
-      <c r="K251" t="s">
-        <v>2525</v>
-      </c>
-      <c r="L251" s="10" t="s">
-        <v>2526</v>
-      </c>
-      <c r="M251" s="8" t="s">
-        <v>2527</v>
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>2528</v>
+        <v>2524</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>2529</v>
+        <v>2525</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>54</v>
@@ -19038,33 +19038,33 @@
         <v>55</v>
       </c>
       <c r="G252" s="1" t="s">
+        <v>2526</v>
+      </c>
+      <c r="H252" s="10" t="s">
+        <v>2527</v>
+      </c>
+      <c r="I252" t="s">
+        <v>2528</v>
+      </c>
+      <c r="J252" t="s">
+        <v>2529</v>
+      </c>
+      <c r="K252" t="s">
         <v>2530</v>
       </c>
-      <c r="H252" s="10" t="s">
+      <c r="L252" s="10" t="s">
         <v>2531</v>
       </c>
-      <c r="I252" t="s">
+      <c r="M252" t="s">
         <v>2532</v>
-      </c>
-      <c r="J252" t="s">
-        <v>2533</v>
-      </c>
-      <c r="K252" t="s">
-        <v>2534</v>
-      </c>
-      <c r="L252" s="10" t="s">
-        <v>2535</v>
-      </c>
-      <c r="M252" t="s">
-        <v>2536</v>
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>2537</v>
+        <v>2533</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>2538</v>
+        <v>2534</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>54</v>
@@ -19073,33 +19073,33 @@
         <v>55</v>
       </c>
       <c r="G253" s="1" t="s">
+        <v>2535</v>
+      </c>
+      <c r="H253" s="10" t="s">
+        <v>2536</v>
+      </c>
+      <c r="I253" t="s">
+        <v>2537</v>
+      </c>
+      <c r="J253" s="10" t="s">
+        <v>2538</v>
+      </c>
+      <c r="K253" t="s">
         <v>2539</v>
       </c>
-      <c r="H253" s="10" t="s">
+      <c r="L253" s="10" t="s">
         <v>2540</v>
       </c>
-      <c r="I253" t="s">
+      <c r="M253" t="s">
         <v>2541</v>
-      </c>
-      <c r="J253" s="10" t="s">
-        <v>2542</v>
-      </c>
-      <c r="K253" t="s">
-        <v>2543</v>
-      </c>
-      <c r="L253" s="10" t="s">
-        <v>2544</v>
-      </c>
-      <c r="M253" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>2546</v>
+        <v>2542</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>2547</v>
+        <v>2543</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>54</v>
@@ -19108,33 +19108,33 @@
         <v>55</v>
       </c>
       <c r="G254" s="1" t="s">
+        <v>2544</v>
+      </c>
+      <c r="H254" s="10" t="s">
+        <v>2545</v>
+      </c>
+      <c r="I254" t="s">
+        <v>2546</v>
+      </c>
+      <c r="J254" t="s">
+        <v>2547</v>
+      </c>
+      <c r="K254" t="s">
         <v>2548</v>
       </c>
-      <c r="H254" s="10" t="s">
+      <c r="L254" s="10" t="s">
         <v>2549</v>
       </c>
-      <c r="I254" t="s">
+      <c r="M254" t="s">
         <v>2550</v>
-      </c>
-      <c r="J254" t="s">
-        <v>2551</v>
-      </c>
-      <c r="K254" t="s">
-        <v>2552</v>
-      </c>
-      <c r="L254" s="10" t="s">
-        <v>2553</v>
-      </c>
-      <c r="M254" t="s">
-        <v>2554</v>
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>2555</v>
+        <v>2551</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>2556</v>
+        <v>2552</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>54</v>
@@ -19143,30 +19143,30 @@
         <v>55</v>
       </c>
       <c r="H255" s="10" t="s">
+        <v>2553</v>
+      </c>
+      <c r="I255" s="10" t="s">
+        <v>2554</v>
+      </c>
+      <c r="J255" t="s">
+        <v>2555</v>
+      </c>
+      <c r="K255" t="s">
+        <v>2556</v>
+      </c>
+      <c r="L255" s="10" t="s">
         <v>2557</v>
       </c>
-      <c r="I255" s="10" t="s">
+      <c r="M255" s="22" t="s">
         <v>2558</v>
-      </c>
-      <c r="J255" t="s">
-        <v>2559</v>
-      </c>
-      <c r="K255" t="s">
-        <v>2560</v>
-      </c>
-      <c r="L255" s="10" t="s">
-        <v>2561</v>
-      </c>
-      <c r="M255" s="22" t="s">
-        <v>2562</v>
       </c>
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>2563</v>
+        <v>2559</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>2564</v>
+        <v>2560</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>54</v>
@@ -19177,10 +19177,10 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>2565</v>
+        <v>2561</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>2566</v>
+        <v>2562</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>54</v>
@@ -19191,10 +19191,10 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>2567</v>
+        <v>2563</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>2568</v>
+        <v>2564</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>54</v>
@@ -19207,166 +19207,166 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>2569</v>
+        <v>2565</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>2570</v>
+        <v>2566</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>2571</v>
+        <v>2567</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>2572</v>
+        <v>2568</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="K260" s="2"/>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>2573</v>
+        <v>2569</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>2574</v>
+        <v>2570</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>2575</v>
+        <v>2571</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>2576</v>
+        <v>2572</v>
       </c>
       <c r="E262" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>2577</v>
+        <v>2573</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>2578</v>
+        <v>2574</v>
       </c>
       <c r="E263" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>2579</v>
+        <v>2575</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>2580</v>
+        <v>2576</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>2581</v>
+        <v>2577</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>2582</v>
+        <v>2578</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
       <c r="K265" s="2"/>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>2583</v>
+        <v>2579</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>2584</v>
+        <v>2580</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>2585</v>
+        <v>2581</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>2586</v>
+        <v>2582</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>2587</v>
+        <v>2583</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>2588</v>
+        <v>2584</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>2589</v>
+        <v>2585</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>2590</v>
+        <v>2586</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>2286</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>2591</v>
+        <v>2587</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>2592</v>
+        <v>2588</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>966</v>
@@ -19377,10 +19377,10 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>2593</v>
+        <v>2589</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>2594</v>
+        <v>2590</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>966</v>
@@ -19391,10 +19391,10 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>2595</v>
+        <v>2591</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>966</v>
@@ -19405,10 +19405,10 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>2597</v>
+        <v>2593</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>2598</v>
+        <v>2594</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>966</v>
@@ -19419,10 +19419,10 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>2599</v>
+        <v>2595</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>2600</v>
+        <v>2596</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>966</v>
@@ -19433,10 +19433,10 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
-        <v>2601</v>
+        <v>2597</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>2602</v>
+        <v>2598</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>966</v>
@@ -19447,10 +19447,10 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>2603</v>
+        <v>2599</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>2604</v>
+        <v>2600</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>966</v>
@@ -19461,24 +19461,24 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>2605</v>
+        <v>2601</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>2606</v>
+        <v>2602</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>2607</v>
+        <v>2603</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>2608</v>
+        <v>2604</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>240</v>
@@ -19489,24 +19489,24 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>2609</v>
+        <v>2605</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>2610</v>
+        <v>2606</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>2611</v>
+        <v>2607</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>2612</v>
+        <v>2608</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>966</v>
@@ -19517,178 +19517,178 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>2613</v>
+        <v>2609</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>2614</v>
+        <v>2610</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>2615</v>
+        <v>2611</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>2616</v>
+        <v>2612</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>2617</v>
+        <v>2613</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>2618</v>
+        <v>2614</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>2619</v>
+        <v>2615</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>2620</v>
+        <v>2616</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
-        <v>2621</v>
+        <v>2617</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>2622</v>
+        <v>2618</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
-        <v>2623</v>
+        <v>2619</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>2624</v>
+        <v>2620</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>2625</v>
+        <v>2621</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>2626</v>
+        <v>2622</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>2627</v>
+        <v>2623</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>2628</v>
+        <v>2624</v>
       </c>
       <c r="E288" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
-        <v>2629</v>
+        <v>2625</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>2630</v>
+        <v>2626</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>2631</v>
+        <v>2627</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>2632</v>
+        <v>2628</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
-        <v>2633</v>
+        <v>2629</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>2634</v>
+        <v>2630</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
-        <v>2635</v>
+        <v>2631</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>2636</v>
+        <v>2632</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
-        <v>2637</v>
+        <v>2633</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>2638</v>
+        <v>2634</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>714</v>
@@ -19699,10 +19699,10 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
-        <v>2639</v>
+        <v>2635</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>2640</v>
+        <v>2636</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>714</v>
@@ -19713,10 +19713,10 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
-        <v>2641</v>
+        <v>2637</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>2642</v>
+        <v>2638</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>714</v>
@@ -19727,10 +19727,10 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>2643</v>
+        <v>2639</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>2644</v>
+        <v>2640</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>714</v>
@@ -19741,10 +19741,10 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>2645</v>
+        <v>2641</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>2646</v>
+        <v>2642</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>714</v>
@@ -19755,10 +19755,10 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>2647</v>
+        <v>2643</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>2648</v>
+        <v>2644</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>714</v>
@@ -19769,10 +19769,10 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>2649</v>
+        <v>2645</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>2650</v>
+        <v>2646</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>714</v>
@@ -19783,458 +19783,458 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
-        <v>2651</v>
+        <v>2647</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>2652</v>
+        <v>2648</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>2653</v>
+        <v>2649</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>2654</v>
+        <v>2650</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>2655</v>
+        <v>2651</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>2656</v>
+        <v>2652</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>2657</v>
+        <v>2653</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>2658</v>
+        <v>2654</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>2659</v>
+        <v>2655</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>2660</v>
+        <v>2656</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>2661</v>
+        <v>2657</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>2662</v>
+        <v>2658</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>2663</v>
+        <v>2659</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>2664</v>
+        <v>2660</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>2665</v>
+        <v>2661</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>2666</v>
+        <v>2662</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>2667</v>
+        <v>2663</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>2668</v>
+        <v>2664</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>2669</v>
+        <v>2665</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>2670</v>
+        <v>2666</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>2672</v>
+        <v>2668</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>2673</v>
+        <v>2669</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
-        <v>2674</v>
+        <v>2670</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>2675</v>
+        <v>2671</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>2676</v>
+        <v>2672</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>2677</v>
+        <v>2673</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
-        <v>2678</v>
+        <v>2674</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>2679</v>
+        <v>2675</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>2680</v>
+        <v>2676</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>2682</v>
+        <v>2678</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>2683</v>
+        <v>2679</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>2684</v>
+        <v>2680</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>2685</v>
+        <v>2681</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>2686</v>
+        <v>2682</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>2687</v>
+        <v>2683</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>2689</v>
+        <v>2685</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
-        <v>2690</v>
+        <v>2686</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>2691</v>
+        <v>2687</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>2671</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>2692</v>
+        <v>2688</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>2695</v>
+        <v>2691</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>2696</v>
+        <v>2692</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>2697</v>
+        <v>2693</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
-        <v>2698</v>
+        <v>2694</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
-        <v>2699</v>
+        <v>2695</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
-        <v>2700</v>
+        <v>2696</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
-        <v>2701</v>
+        <v>2697</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
-        <v>2702</v>
+        <v>2698</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
-        <v>2703</v>
+        <v>2699</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
-        <v>2704</v>
+        <v>2700</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
-        <v>2705</v>
+        <v>2701</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
-        <v>2706</v>
+        <v>2702</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
-        <v>2707</v>
+        <v>2703</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
-        <v>2708</v>
+        <v>2704</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>2709</v>
+        <v>2705</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
-        <v>2710</v>
+        <v>2706</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>391</v>
@@ -20245,7 +20245,7 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
-        <v>2711</v>
+        <v>2707</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>391</v>
@@ -20256,7 +20256,7 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
-        <v>2712</v>
+        <v>2708</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>391</v>
@@ -20267,7 +20267,7 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
-        <v>2713</v>
+        <v>2709</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>391</v>
@@ -20278,7 +20278,7 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
-        <v>2714</v>
+        <v>2710</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>391</v>
@@ -20289,7 +20289,7 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
-        <v>2715</v>
+        <v>2711</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>391</v>
@@ -20300,7 +20300,7 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
-        <v>2716</v>
+        <v>2712</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>391</v>
@@ -20311,7 +20311,7 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
-        <v>2717</v>
+        <v>2713</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>391</v>
@@ -20322,7 +20322,7 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
-        <v>2718</v>
+        <v>2714</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>391</v>
@@ -20333,7 +20333,7 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
-        <v>2719</v>
+        <v>2715</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>391</v>
@@ -20344,7 +20344,7 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
-        <v>2720</v>
+        <v>2716</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>391</v>
@@ -20355,7 +20355,7 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
-        <v>2721</v>
+        <v>2717</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>391</v>
@@ -20366,7 +20366,7 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
-        <v>2722</v>
+        <v>2718</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>391</v>
@@ -20377,7 +20377,7 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
-        <v>2723</v>
+        <v>2719</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>391</v>
@@ -20388,7 +20388,7 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
-        <v>2724</v>
+        <v>2720</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>240</v>
@@ -20399,7 +20399,7 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
-        <v>2725</v>
+        <v>2721</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>240</v>
@@ -20410,7 +20410,7 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
-        <v>2726</v>
+        <v>2722</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>240</v>
@@ -20421,7 +20421,7 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
-        <v>2727</v>
+        <v>2723</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>240</v>
@@ -20432,7 +20432,7 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
-        <v>2728</v>
+        <v>2724</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>240</v>
@@ -20443,7 +20443,7 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
-        <v>2729</v>
+        <v>2725</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>240</v>
@@ -20454,7 +20454,7 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
-        <v>2730</v>
+        <v>2726</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>240</v>
@@ -20465,7 +20465,7 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>240</v>
@@ -20476,7 +20476,7 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
-        <v>2732</v>
+        <v>2728</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>240</v>
@@ -20487,62 +20487,62 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
-        <v>2733</v>
+        <v>2729</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
-        <v>2734</v>
+        <v>2730</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
-        <v>2735</v>
+        <v>2731</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
-        <v>2736</v>
+        <v>2732</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
-        <v>2737</v>
+        <v>2733</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
-        <v>2738</v>
+        <v>2734</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>966</v>
@@ -20553,7 +20553,7 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
-        <v>2739</v>
+        <v>2735</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>966</v>
@@ -20564,7 +20564,7 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>966</v>
@@ -20575,7 +20575,7 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
-        <v>2741</v>
+        <v>2737</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>966</v>
@@ -20586,7 +20586,7 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
-        <v>2742</v>
+        <v>2738</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>966</v>
@@ -20597,7 +20597,7 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
-        <v>2743</v>
+        <v>2739</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>966</v>
@@ -20608,7 +20608,7 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
-        <v>2744</v>
+        <v>2740</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>966</v>
@@ -20619,7 +20619,7 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
-        <v>2745</v>
+        <v>2741</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>966</v>
@@ -20630,7 +20630,7 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="s">
-        <v>2746</v>
+        <v>2742</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>966</v>
@@ -20641,7 +20641,7 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
-        <v>2747</v>
+        <v>2743</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>966</v>
@@ -20652,7 +20652,7 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="s">
-        <v>2748</v>
+        <v>2744</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>966</v>
@@ -20663,7 +20663,7 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
-        <v>2749</v>
+        <v>2745</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>966</v>
@@ -20674,7 +20674,7 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
-        <v>2750</v>
+        <v>2746</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>966</v>
@@ -20685,7 +20685,7 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
-        <v>2751</v>
+        <v>2747</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>966</v>
@@ -20696,7 +20696,7 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
-        <v>2752</v>
+        <v>2748</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>966</v>
@@ -20707,7 +20707,7 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
-        <v>2753</v>
+        <v>2749</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>966</v>
@@ -20718,7 +20718,7 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
-        <v>2754</v>
+        <v>2750</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>966</v>
@@ -20729,7 +20729,7 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
-        <v>2755</v>
+        <v>2751</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>966</v>
@@ -20740,7 +20740,7 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
-        <v>2756</v>
+        <v>2752</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>966</v>
@@ -20751,7 +20751,7 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
-        <v>2757</v>
+        <v>2753</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>966</v>
@@ -20762,161 +20762,161 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
-        <v>2758</v>
+        <v>2754</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
-        <v>2759</v>
+        <v>2755</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
-        <v>2760</v>
+        <v>2756</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
-        <v>2761</v>
+        <v>2757</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
-        <v>2762</v>
+        <v>2758</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
-        <v>2763</v>
+        <v>2759</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
-        <v>2764</v>
+        <v>2760</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
-        <v>2765</v>
+        <v>2761</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
-        <v>2766</v>
+        <v>2762</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1872</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
-        <v>2767</v>
+        <v>2763</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1872</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
-        <v>2768</v>
+        <v>2764</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1872</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
-        <v>2769</v>
+        <v>2765</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>1872</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
-        <v>2770</v>
+        <v>2766</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>1872</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
-        <v>2771</v>
+        <v>2767</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>1872</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
-        <v>2772</v>
+        <v>2768</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>15</v>
@@ -20927,7 +20927,7 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
-        <v>2773</v>
+        <v>2769</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>15</v>
@@ -20938,7 +20938,7 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
-        <v>2774</v>
+        <v>2770</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>15</v>
@@ -20949,7 +20949,7 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
-        <v>2775</v>
+        <v>2771</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>15</v>
@@ -20960,7 +20960,7 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
-        <v>2776</v>
+        <v>2772</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>15</v>
@@ -20971,7 +20971,7 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
-        <v>2777</v>
+        <v>2773</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>15</v>
@@ -20982,7 +20982,7 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
-        <v>2778</v>
+        <v>2774</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>15</v>
@@ -20993,7 +20993,7 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
-        <v>2779</v>
+        <v>2775</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>15</v>
@@ -21004,7 +21004,7 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
-        <v>2780</v>
+        <v>2776</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>15</v>
@@ -21015,7 +21015,7 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
-        <v>2781</v>
+        <v>2777</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>15</v>
@@ -21026,7 +21026,7 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
-        <v>2782</v>
+        <v>2778</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>15</v>
@@ -21037,7 +21037,7 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
-        <v>2783</v>
+        <v>2779</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>15</v>
@@ -21048,7 +21048,7 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
-        <v>2784</v>
+        <v>2780</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>15</v>
@@ -21059,7 +21059,7 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
-        <v>2785</v>
+        <v>2781</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>15</v>
@@ -21070,7 +21070,7 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
-        <v>2786</v>
+        <v>2782</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>15</v>
@@ -21081,7 +21081,7 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
-        <v>2787</v>
+        <v>2783</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>15</v>
@@ -21092,7 +21092,7 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
-        <v>2788</v>
+        <v>2784</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>15</v>
@@ -21103,7 +21103,7 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
-        <v>2789</v>
+        <v>2785</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>15</v>
@@ -21114,29 +21114,29 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
-        <v>2790</v>
+        <v>2786</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
-        <v>2792</v>
+        <v>2788</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
-        <v>2793</v>
+        <v>2789</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>102</v>
@@ -21147,29 +21147,29 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
-        <v>2794</v>
+        <v>2790</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
-        <v>2795</v>
+        <v>2791</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
-        <v>2796</v>
+        <v>2792</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>102</v>
@@ -21180,7 +21180,7 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
-        <v>2797</v>
+        <v>2793</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>102</v>
@@ -21191,7 +21191,7 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
-        <v>2798</v>
+        <v>2794</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>102</v>
@@ -21202,51 +21202,51 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
-        <v>2799</v>
+        <v>2795</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
-        <v>2800</v>
+        <v>2796</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
-        <v>2801</v>
+        <v>2797</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
-        <v>2802</v>
+        <v>2798</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
-        <v>2803</v>
+        <v>2799</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>102</v>
@@ -21257,7 +21257,7 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
-        <v>2804</v>
+        <v>2800</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>102</v>
@@ -21268,7 +21268,7 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
-        <v>2805</v>
+        <v>2801</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>102</v>
@@ -21279,7 +21279,7 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
-        <v>2806</v>
+        <v>2802</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>102</v>
@@ -21290,7 +21290,7 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
-        <v>2807</v>
+        <v>2803</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>102</v>
@@ -21301,7 +21301,7 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
-        <v>2808</v>
+        <v>2804</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>102</v>
@@ -21312,7 +21312,7 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
-        <v>2809</v>
+        <v>2805</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>102</v>
@@ -21323,568 +21323,568 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
-        <v>2810</v>
+        <v>2806</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
-        <v>2811</v>
+        <v>2807</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
-        <v>2812</v>
+        <v>2808</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
-        <v>2814</v>
+        <v>2810</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
-        <v>2815</v>
+        <v>2811</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
-        <v>2816</v>
+        <v>2812</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
-        <v>2817</v>
+        <v>2813</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
-        <v>2818</v>
+        <v>2814</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
-        <v>2819</v>
+        <v>2815</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
-        <v>2820</v>
+        <v>2816</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
-        <v>2821</v>
+        <v>2817</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
-        <v>2822</v>
+        <v>2818</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
-        <v>2823</v>
+        <v>2819</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
-        <v>2824</v>
+        <v>2820</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
-        <v>2825</v>
+        <v>2821</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
-        <v>2826</v>
+        <v>2822</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
-        <v>2827</v>
+        <v>2823</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
-        <v>2828</v>
+        <v>2824</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
-        <v>2829</v>
+        <v>2825</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
-        <v>2830</v>
+        <v>2826</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
-        <v>2831</v>
+        <v>2827</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
-        <v>2832</v>
+        <v>2828</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
-        <v>2833</v>
+        <v>2829</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
-        <v>2834</v>
+        <v>2830</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
-        <v>2835</v>
+        <v>2831</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
-        <v>2836</v>
+        <v>2832</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
-        <v>2837</v>
+        <v>2833</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="s">
-        <v>2838</v>
+        <v>2834</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
-        <v>2839</v>
+        <v>2835</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
-        <v>2840</v>
+        <v>2836</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A465" s="1" t="s">
-        <v>2841</v>
+        <v>2837</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
-        <v>2842</v>
+        <v>2838</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
-        <v>2843</v>
+        <v>2839</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
-        <v>2844</v>
+        <v>2840</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
-        <v>2845</v>
+        <v>2841</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
-        <v>2846</v>
+        <v>2842</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
-        <v>2847</v>
+        <v>2843</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="s">
-        <v>2848</v>
+        <v>2844</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>391</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="s">
-        <v>2849</v>
+        <v>2845</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
-        <v>2850</v>
+        <v>2846</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
-        <v>2851</v>
+        <v>2847</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="s">
-        <v>2852</v>
+        <v>2848</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="s">
-        <v>2853</v>
+        <v>2849</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="s">
-        <v>2854</v>
+        <v>2850</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="s">
-        <v>2855</v>
+        <v>2851</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="s">
-        <v>2856</v>
+        <v>2852</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
-        <v>2857</v>
+        <v>2853</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>714</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="s">
-        <v>2858</v>
+        <v>2854</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="s">
-        <v>2859</v>
+        <v>2855</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="s">
-        <v>2860</v>
+        <v>2856</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>102</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>2791</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="s">
-        <v>2861</v>
+        <v>2857</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>102</v>
@@ -21895,7 +21895,7 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="s">
-        <v>2862</v>
+        <v>2858</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>102</v>
@@ -21906,62 +21906,62 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="s">
-        <v>2863</v>
+        <v>2859</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A488" s="1" t="s">
-        <v>2864</v>
+        <v>2860</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="s">
-        <v>2865</v>
+        <v>2861</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="s">
-        <v>2866</v>
+        <v>2862</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="s">
-        <v>2867</v>
+        <v>2863</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>2224</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="s">
-        <v>2868</v>
+        <v>2864</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>240</v>
@@ -21972,7 +21972,7 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
-        <v>2869</v>
+        <v>2865</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>240</v>
@@ -21983,7 +21983,7 @@
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
-        <v>2870</v>
+        <v>2866</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>240</v>
@@ -21994,7 +21994,7 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="s">
-        <v>2871</v>
+        <v>2867</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>966</v>
@@ -22005,322 +22005,322 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="s">
-        <v>2872</v>
+        <v>2868</v>
       </c>
       <c r="E496" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="s">
-        <v>2873</v>
+        <v>2869</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="s">
-        <v>2874</v>
+        <v>2870</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="s">
-        <v>2875</v>
+        <v>2871</v>
       </c>
       <c r="E499" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F499" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="s">
-        <v>2876</v>
+        <v>2872</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="s">
-        <v>2877</v>
+        <v>2873</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="s">
-        <v>2878</v>
+        <v>2874</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="s">
-        <v>2879</v>
+        <v>2875</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A504" s="1" t="s">
-        <v>2880</v>
+        <v>2876</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A505" s="1" t="s">
-        <v>2881</v>
+        <v>2877</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A506" s="1" t="s">
-        <v>2882</v>
+        <v>2878</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A507" s="1" t="s">
-        <v>2883</v>
+        <v>2879</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A508" s="1" t="s">
-        <v>2884</v>
+        <v>2880</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F508" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="s">
-        <v>2885</v>
+        <v>2881</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F509" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="s">
-        <v>2886</v>
+        <v>2882</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F510" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A511" s="1" t="s">
-        <v>2887</v>
+        <v>2883</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F511" s="1" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A512" s="1" t="s">
-        <v>2888</v>
+        <v>2884</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>2889</v>
+        <v>2885</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F512" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A513" s="1" t="s">
-        <v>2890</v>
+        <v>2886</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>2891</v>
+        <v>2887</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A514" s="1" t="s">
-        <v>2892</v>
+        <v>2888</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F514" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A515" s="1" t="s">
-        <v>2893</v>
+        <v>2889</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F515" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A516" s="1" t="s">
-        <v>2894</v>
+        <v>2890</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A517" s="1" t="s">
-        <v>2895</v>
+        <v>2891</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A518" s="1" t="s">
-        <v>2896</v>
+        <v>2892</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A519" s="1" t="s">
-        <v>2897</v>
+        <v>2893</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A520" s="1" t="s">
-        <v>2898</v>
+        <v>2894</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A521" s="1" t="s">
-        <v>2899</v>
+        <v>2895</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A522" s="1" t="s">
-        <v>2900</v>
+        <v>2896</v>
       </c>
       <c r="E522" s="1" t="s">
         <v>240</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>1747</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A523" s="1" t="s">
-        <v>2901</v>
+        <v>2897</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>2902</v>
+        <v>2898</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>54</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G523" s="1" t="s">
-        <v>2903</v>
+        <v>2899</v>
       </c>
       <c r="H523" s="2"/>
     </row>
@@ -22376,7 +22376,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>2904</v>
+        <v>2900</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>10</v>
@@ -22388,230 +22388,230 @@
         <v>12</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>2905</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>2906</v>
+        <v>2902</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>2907</v>
+        <v>2903</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
         <v>54</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>2909</v>
+        <v>2905</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>2910</v>
+        <v>2906</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>2911</v>
+        <v>2907</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>2912</v>
+        <v>2908</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5" t="s">
-        <v>2913</v>
+        <v>2909</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>2914</v>
+        <v>2910</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>2915</v>
+        <v>2911</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>2916</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>2917</v>
+        <v>2913</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2918</v>
+        <v>2914</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>2919</v>
+        <v>2915</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
         <v>54</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>2920</v>
+        <v>2916</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>2921</v>
+        <v>2917</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>2922</v>
+        <v>2918</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>2923</v>
+        <v>2919</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5" t="s">
-        <v>2924</v>
+        <v>2920</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>2925</v>
+        <v>2921</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>2926</v>
+        <v>2922</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>2927</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>2928</v>
+        <v>2924</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>2929</v>
+        <v>2925</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>2930</v>
+        <v>2926</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
         <v>54</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>2931</v>
+        <v>2927</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>2932</v>
+        <v>2928</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>2933</v>
+        <v>2929</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>2934</v>
+        <v>2930</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5" t="s">
-        <v>2935</v>
+        <v>2931</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>2936</v>
+        <v>2932</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>2937</v>
+        <v>2933</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>2938</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>2939</v>
+        <v>2935</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>2940</v>
+        <v>2936</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>2941</v>
+        <v>2937</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
         <v>54</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>2942</v>
+        <v>2938</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>2943</v>
+        <v>2939</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>2944</v>
+        <v>2940</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>2945</v>
+        <v>2941</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5" t="s">
-        <v>2946</v>
+        <v>2942</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>2947</v>
+        <v>2943</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>2948</v>
+        <v>2944</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>2949</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>2950</v>
+        <v>2946</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>2951</v>
+        <v>2947</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>2952</v>
+        <v>2948</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>2953</v>
+        <v>2949</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>2955</v>
+        <v>2951</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>2956</v>
+        <v>2952</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
-        <v>2957</v>
+        <v>2953</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>2958</v>
+        <v>2954</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>2959</v>
+        <v>2955</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>2960</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>2961</v>
+        <v>2957</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2962</v>
+        <v>2958</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -22619,32 +22619,32 @@
         <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>2235</v>
+        <v>2231</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>2963</v>
+        <v>2959</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>2964</v>
+        <v>2960</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>2965</v>
+        <v>2961</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>2966</v>
+        <v>2962</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5" t="s">
-        <v>2967</v>
+        <v>2963</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>2968</v>
+        <v>2964</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>2969</v>
+        <v>2965</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>2970</v>
+        <v>2966</v>
       </c>
     </row>
   </sheetData>
